--- a/app/excel_files/precos_composicoes_insumos.xlsx
+++ b/app/excel_files/precos_composicoes_insumos.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\sinapi+\app\excel_files\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE368C69-FE9A-48E2-B96F-4C4DFFB9B019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Planilha1!$A$1:$AE$1842</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$AF$1842</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,325 +28,310 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="96">
-  <si>
-    <t xml:space="preserve">grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo_da_composicao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">descricao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">al</t>
-  </si>
-  <si>
-    <t xml:space="preserve">am</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">es</t>
-  </si>
-  <si>
-    <t xml:space="preserve">go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">to</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATERIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC DEFOFO, JEI, 1 MPA, DN 150 MM, PARA REDE DE AGUA (NBR 7665)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC DEFOFO, JEI, 1 MPA, DN 200 MM, PARA REDE DE AGUA (NBR 7665)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC DEFOFO, JEI, 1 MPA, DN 250 MM, PARA REDE DE AGUA (NBR 7665)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC DEFOFO, JEI, 1 MPA, DN 300 MM, PARA REDE DE AGUA (NBR 7665)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC PBA JEI, CLASSE 15, DN 100 MM, PARA REDE DE AGUA (NBR 5647)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC PBA JEI, CLASSE 15, DN 50 MM, PARA REDE DE AGUA (NBR 5647)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO PVC PBA JEI, CLASSE 15, DN 75 MM, PARA REDE DE AGUA (NBR 5647)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assentamento de Tubos de Esgoto em PVC e PEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 100 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 150 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 200 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 250 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 300 MM, JUNTA ELÁSTICA, FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 350 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 400 MM, JUNTA ELÁSTICA FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assentamento de Tubos de PVC e Metálicos em Redes de Água</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 150 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 200 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 250 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 300 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC PBA PARA REDE DE ÁGUA, DN 100 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC PBA PARA REDE DE ÁGUA, DN 50 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTAMENTO DE TUBO DE PVC PBA PARA REDE DE ÁGUA, DN 75 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aterro e Reaterro de Valas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REATERRO MANUAL DE VALAS, COM COMPACTADOR DE SOLOS DE PERCUSSÃO. AF_08/2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REATERRO MECANIZADO DE VALA COM RETROESCAVADEIRA (CAPACIDADE DA CAÇAMBA DA RETRO: 0,26 M³/POTÊNCIA: 88 HP), LARGURA ATÉ 0,8 M, PROFUNDIDADE 1,5 A 3,0 M, COM SOLO (SEM SUBSTITUIÇÃO) DE 1ª CATEGORIA, COM COMPACTADOR DE SOLOS DE PERCUSSÃO AF_08/2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REATERRO MECANIZADO DE VALA COM RETROESCAVADEIRA (CAPACIDADE DA CAÇAMBA DA RETRO: 0,26 M³/POTÊNCIA: 88 HP), LARGURA ATÉ 0,8 M, PROFUNDIDADE ATÉ 1,5 M, COM SOLO (SEM SUBSTITUIÇÃO) DE 1ª CATEGORIA, COM COMPACTADOR DE SOLOS DE PERCUSSÃO. AF_08/2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caixas Enterradas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAMPA CIRCULAR PARA ESGOTO E DRENAGEM, EM FERRO FUNDIDO, DIÂMETRO INTERNO = 0,6 M. AF_12/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escavação de Valas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCAVAÇÃO MECANIZADA DE VALA COM PROF. ATÉ 1,5 M (MÉDIA MONTANTE E JUSANTE/UMA COMPOSIÇÃO POR TRECHO), RETROESCAV. (0,26 M3), LARG. MENOR QUE 0,8 M, EM SOLO DE 1A CATEGORIA, EM LOCAIS COM ALTO NÍVEL DE INTERFERÊNCIA. AF_09/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCAVAÇÃO MECANIZADA DE VALA COM PROFUNDIDADE ATÉ 1,5 M (MÉDIA MONTANTE E JUSANTE/UMA COMPOSIÇÃO POR TRECHO), RETROESCAV. (0,26 M3), LARGURA MENOR QUE 0,8 M, EM SOLO DE 1A CATEGORIA, LOCAIS COM BAIXO NÍVEL DE INTERFERÊNCIA. AF_09/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escoramento e Preparo de Fundo de Valas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCORAMENTO DE VALA, TIPO DESCONTÍNUO, COM PROFUNDIDADE DE 0 A 1,5 M, LARGURA MENOR QUE 1,5 M. AF_08/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCORAMENTO DE VALA, TIPO DESCONTÍNUO, COM PROFUNDIDADE DE 1,5 M A 3,0 M, LARGURA MENOR QUE 1,5 M. AF_08/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCORAMENTO DE VALA, TIPO PONTALETEAMENTO, COM PROFUNDIDADE DE 0 A 1,5 M, LARGURA MENOR QUE 1,5 M. AF_08/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREPARO DE FUNDO DE VALA COM LARGURA MENOR QUE 1,5 M, COM CAMADA DE AREIA, LANÇAMENTO MECANIZADO. AF_08/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligações Prediais de Água e Esgoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLAR DE TOMADA, PVC, COM TRAVAS, DE 60 MM X 1/2" OU 60 MM X 3/4", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO/JOELHO COM ADAPTADOR, POLIPROPILENO, PARA TUBOS EM PEAD, 20 MM X 1/2", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA LONGA, 90 GRAUS, PVC OCRE, JUNTA ELÁSTICA, DN 100 MM, PARA COLETOR PREDIAL DE ESGOTO. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA, PVC, ROSCÁVEL, 1/2", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGISTRO ESFERA, PVC, COM ROSCA, 1/2", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELIM, PVC OCRE, COM TRAVA, DN 125 X 100 MM OU 150 X 100 MM, PARA COLETOR PREDIAL DE ESGOTO. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO, PEAD, PE-80, DE = 20 MM X 2,3 MM, PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO, PVC OCRE, JUNTA ELÁSTICA, DN 100 MM, PARA COLETOR PREDIAL DE ESGOTO. AF_06/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Locação de Obras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOCAÇÃO DE REDE DE ÁGUA OU ESGOTO. AF_03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poços de Visita e Caixas para Bocas de Lobo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACRÉSCIMO PARA POÇO DE VISITA CIRCULAR PARA ESGOTO, EM CONCRETO PRÉ-MOLDADO, DIÂMETRO INTERNO = 1 M. AF_12/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASE PARA POÇO DE VISITA CIRCULAR PARA ESGOTO, EM CONCRETO PRÉ-MOLDADO, DIÂMETRO INTERNO = 1,0 M, PROFUNDIDADE = 1,35 M, EXCLUINDO TAMPÃO. AF_12/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAMINÉ CIRCULAR PARA POÇO DE VISITA PARA ESGOTO, EM CONCRETO PRÉ-MOLDADO, DIÂMETRO INTERNO = 0,6 M. AF_12/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sistemas de Medição</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA EM CONCRETO PRÉ-MOLDADO PARA ABRIGO DE HIDRÔMETRO COM DN 20 MM - FORNECIMENTO E INSTALAÇÃO. AF_03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIDRÔMETRO DN 1/2", 1,5 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT CAVALETE PARA MEDIÇÃO DE ÁGUA - ENTRADA PRINCIPAL, EM PVC 20 MM (1/2") - FORNECIMENTO E INSTALAÇÃO (EXCLUSIVE HIDRÔMETRO). AF_03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transporte, Carga e Descarga de Materiais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARGA, MANOBRA E DESCARGA DE SOLOS E MATERIAIS GRANULARES EM CAMINHÃO BASCULANTE 6 M³ - CARGA COM ESCAVADEIRA HIDRÁULICA (CAÇAMBA DE 1,20 M³ / 155 HP) E DESCARGA LIVRE (UNIDADE: M3). AF_07/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRANSPORTE COM CAMINHÃO BASCULANTE DE 6 M³, EM VIA URBANA PAVIMENTADA, DMT ATÉ 30 KM (UNIDADE: M3XKM). AF_07/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3XKM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="97">
+  <si>
+    <t>grupo</t>
+  </si>
+  <si>
+    <t>codigo_da_composicao</t>
+  </si>
+  <si>
+    <t>descricao</t>
+  </si>
+  <si>
+    <t>unidade</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>ba</t>
+  </si>
+  <si>
+    <t>ce</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>go</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>mg</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>mt</t>
+  </si>
+  <si>
+    <t>pa</t>
+  </si>
+  <si>
+    <t>pb</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>pi</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>rj</t>
+  </si>
+  <si>
+    <t>rn</t>
+  </si>
+  <si>
+    <t>ro</t>
+  </si>
+  <si>
+    <t>rr</t>
+  </si>
+  <si>
+    <t>rs</t>
+  </si>
+  <si>
+    <t>sc</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+  </si>
+  <si>
+    <t>TUBO PVC DEFOFO, JEI, 1 MPA, DN 150 MM, PARA REDE DE AGUA (NBR 7665)</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>TUBO PVC DEFOFO, JEI, 1 MPA, DN 200 MM, PARA REDE DE AGUA (NBR 7665)</t>
+  </si>
+  <si>
+    <t>TUBO PVC DEFOFO, JEI, 1 MPA, DN 250 MM, PARA REDE DE AGUA (NBR 7665)</t>
+  </si>
+  <si>
+    <t>TUBO PVC DEFOFO, JEI, 1 MPA, DN 300 MM, PARA REDE DE AGUA (NBR 7665)</t>
+  </si>
+  <si>
+    <t>TUBO PVC PBA JEI, CLASSE 15, DN 100 MM, PARA REDE DE AGUA (NBR 5647)</t>
+  </si>
+  <si>
+    <t>TUBO PVC PBA JEI, CLASSE 15, DN 50 MM, PARA REDE DE AGUA (NBR 5647)</t>
+  </si>
+  <si>
+    <t>TUBO PVC PBA JEI, CLASSE 15, DN 75 MM, PARA REDE DE AGUA (NBR 5647)</t>
+  </si>
+  <si>
+    <t>Assentamento de Tubos de Esgoto em PVC e PEAD</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 100 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 150 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 200 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 250 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 300 MM, JUNTA ELÁSTICA, FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 350 MM, JUNTA ELÁSTICA - FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>TUBO DE PVC PARA REDE COLETORA DE ESGOTO DE PAREDE MACIÇA, DN 400 MM, JUNTA ELÁSTICA FORNECIMENTO E ASSENTAMENTO. AF_01/2021</t>
+  </si>
+  <si>
+    <t>Assentamento de Tubos de PVC e Metálicos em Redes de Água</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 150 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 200 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 250 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC DEFOFO OU PRFV OU RPVC PARA REDE DE ÁGUA, DN 300 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC PBA PARA REDE DE ÁGUA, DN 100 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC PBA PARA REDE DE ÁGUA, DN 50 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>ASSENTAMENTO DE TUBO DE PVC PBA PARA REDE DE ÁGUA, DN 75 MM, JUNTA ELÁSTICA INTEGRADA, INSTALADO EM LOCAL COM NÍVEL BAIXO DE INTERFERÊNCIAS (NÃO INCLUI FORNECIMENTO). AF_05/2024</t>
+  </si>
+  <si>
+    <t>Aterro e Reaterro de Valas</t>
+  </si>
+  <si>
+    <t>REATERRO MANUAL DE VALAS, COM COMPACTADOR DE SOLOS DE PERCUSSÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>REATERRO MECANIZADO DE VALA COM RETROESCAVADEIRA (CAPACIDADE DA CAÇAMBA DA RETRO: 0,26 M³/POTÊNCIA: 88 HP), LARGURA ATÉ 0,8 M, PROFUNDIDADE 1,5 A 3,0 M, COM SOLO (SEM SUBSTITUIÇÃO) DE 1ª CATEGORIA, COM COMPACTADOR DE SOLOS DE PERCUSSÃO AF_08/2023</t>
+  </si>
+  <si>
+    <t>REATERRO MECANIZADO DE VALA COM RETROESCAVADEIRA (CAPACIDADE DA CAÇAMBA DA RETRO: 0,26 M³/POTÊNCIA: 88 HP), LARGURA ATÉ 0,8 M, PROFUNDIDADE ATÉ 1,5 M, COM SOLO (SEM SUBSTITUIÇÃO) DE 1ª CATEGORIA, COM COMPACTADOR DE SOLOS DE PERCUSSÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t>Caixas Enterradas</t>
+  </si>
+  <si>
+    <t>TAMPA CIRCULAR PARA ESGOTO E DRENAGEM, EM FERRO FUNDIDO, DIÂMETRO INTERNO = 0,6 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>Escavação de Valas</t>
+  </si>
+  <si>
+    <t>ESCAVAÇÃO MECANIZADA DE VALA COM PROF. ATÉ 1,5 M (MÉDIA MONTANTE E JUSANTE/UMA COMPOSIÇÃO POR TRECHO), RETROESCAV. (0,26 M3), LARG. MENOR QUE 0,8 M, EM SOLO DE 1A CATEGORIA, EM LOCAIS COM ALTO NÍVEL DE INTERFERÊNCIA. AF_09/2024</t>
+  </si>
+  <si>
+    <t>ESCAVAÇÃO MECANIZADA DE VALA COM PROFUNDIDADE ATÉ 1,5 M (MÉDIA MONTANTE E JUSANTE/UMA COMPOSIÇÃO POR TRECHO), RETROESCAV. (0,26 M3), LARGURA MENOR QUE 0,8 M, EM SOLO DE 1A CATEGORIA, LOCAIS COM BAIXO NÍVEL DE INTERFERÊNCIA. AF_09/2024</t>
+  </si>
+  <si>
+    <t>Escoramento e Preparo de Fundo de Valas</t>
+  </si>
+  <si>
+    <t>ESCORAMENTO DE VALA, TIPO DESCONTÍNUO, COM PROFUNDIDADE DE 0 A 1,5 M, LARGURA MENOR QUE 1,5 M. AF_08/2020</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>ESCORAMENTO DE VALA, TIPO DESCONTÍNUO, COM PROFUNDIDADE DE 1,5 M A 3,0 M, LARGURA MENOR QUE 1,5 M. AF_08/2020</t>
+  </si>
+  <si>
+    <t>ESCORAMENTO DE VALA, TIPO PONTALETEAMENTO, COM PROFUNDIDADE DE 0 A 1,5 M, LARGURA MENOR QUE 1,5 M. AF_08/2020</t>
+  </si>
+  <si>
+    <t>PREPARO DE FUNDO DE VALA COM LARGURA MENOR QUE 1,5 M, COM CAMADA DE AREIA, LANÇAMENTO MECANIZADO. AF_08/2020</t>
+  </si>
+  <si>
+    <t>Ligações Prediais de Água e Esgoto</t>
+  </si>
+  <si>
+    <t>COLAR DE TOMADA, PVC, COM TRAVAS, DE 60 MM X 1/2" OU 60 MM X 3/4", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
+  </si>
+  <si>
+    <t>COTOVELO/JOELHO COM ADAPTADOR, POLIPROPILENO, PARA TUBOS EM PEAD, 20 MM X 1/2", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
+  </si>
+  <si>
+    <t>CURVA LONGA, 90 GRAUS, PVC OCRE, JUNTA ELÁSTICA, DN 100 MM, PARA COLETOR PREDIAL DE ESGOTO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>LUVA, PVC, ROSCÁVEL, 1/2", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
+  </si>
+  <si>
+    <t>REGISTRO ESFERA, PVC, COM ROSCA, 1/2", PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
+  </si>
+  <si>
+    <t>SELIM, PVC OCRE, COM TRAVA, DN 125 X 100 MM OU 150 X 100 MM, PARA COLETOR PREDIAL DE ESGOTO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>TUBO, PEAD, PE-80, DE = 20 MM X 2,3 MM, PARA LIGAÇÃO PREDIAL DE ÁGUA. AF_06/2022</t>
+  </si>
+  <si>
+    <t>TUBO, PVC OCRE, JUNTA ELÁSTICA, DN 100 MM, PARA COLETOR PREDIAL DE ESGOTO. AF_06/2022</t>
+  </si>
+  <si>
+    <t>Locação de Obras</t>
+  </si>
+  <si>
+    <t>LOCAÇÃO DE REDE DE ÁGUA OU ESGOTO. AF_03/2024</t>
+  </si>
+  <si>
+    <t>Poços de Visita e Caixas para Bocas de Lobo</t>
+  </si>
+  <si>
+    <t>ACRÉSCIMO PARA POÇO DE VISITA CIRCULAR PARA ESGOTO, EM CONCRETO PRÉ-MOLDADO, DIÂMETRO INTERNO = 1 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>BASE PARA POÇO DE VISITA CIRCULAR PARA ESGOTO, EM CONCRETO PRÉ-MOLDADO, DIÂMETRO INTERNO = 1,0 M, PROFUNDIDADE = 1,35 M, EXCLUINDO TAMPÃO. AF_12/2020</t>
+  </si>
+  <si>
+    <t>CHAMINÉ CIRCULAR PARA POÇO DE VISITA PARA ESGOTO, EM CONCRETO PRÉ-MOLDADO, DIÂMETRO INTERNO = 0,6 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t>Sistemas de Medição</t>
+  </si>
+  <si>
+    <t>CAIXA EM CONCRETO PRÉ-MOLDADO PARA ABRIGO DE HIDRÔMETRO COM DN 20 MM - FORNECIMENTO E INSTALAÇÃO. AF_03/2024</t>
+  </si>
+  <si>
+    <t>HIDRÔMETRO DN 1/2", 1,5 M3/H - FORNECIMENTO E INSTALAÇÃO. AF_03/2024</t>
+  </si>
+  <si>
+    <t>KIT CAVALETE PARA MEDIÇÃO DE ÁGUA - ENTRADA PRINCIPAL, EM PVC 20 MM (1/2") - FORNECIMENTO E INSTALAÇÃO (EXCLUSIVE HIDRÔMETRO). AF_03/2024</t>
+  </si>
+  <si>
+    <t>Transporte, Carga e Descarga de Materiais</t>
+  </si>
+  <si>
+    <t>CARGA, MANOBRA E DESCARGA DE SOLOS E MATERIAIS GRANULARES EM CAMINHÃO BASCULANTE 6 M³ - CARGA COM ESCAVADEIRA HIDRÁULICA (CAÇAMBA DE 1,20 M³ / 155 HP) E DESCARGA LIVRE (UNIDADE: M3). AF_07/2020</t>
+  </si>
+  <si>
+    <t>TRANSPORTE COM CAMINHÃO BASCULANTE DE 6 M³, EM VIA URBANA PAVIMENTADA, DMT ATÉ 30 KM (UNIDADE: M3XKM). AF_07/2020</t>
+  </si>
+  <si>
+    <t>M3XKM</t>
+  </si>
+  <si>
+    <t>competencia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -353,7 +343,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -361,138 +351,84 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -524,7 +460,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -548,7 +484,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -608,4710 +544,4851 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:AE49"/>
-  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BN49"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="37.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="20" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="28" style="1" width="10.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="9.82"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="66" style="1" width="8.72"/>
+    <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.85546875" style="1" customWidth="1"/>
+    <col min="8" max="11" width="10.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" style="1" customWidth="1"/>
+    <col min="14" max="15" width="9.85546875" style="1" customWidth="1"/>
+    <col min="16" max="19" width="10.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" style="1" customWidth="1"/>
+    <col min="21" max="23" width="10.85546875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11.85546875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="9.85546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="10.85546875" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.85546875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.85546875" style="1" customWidth="1"/>
+    <col min="29" max="30" width="10.85546875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="9.85546875" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2">
         <v>9828</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F2">
         <v>125.51</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2">
         <v>120.06</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="H2">
         <v>155.38</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="I2">
         <v>129.38</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="J2">
         <v>95.5</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="K2">
         <v>155.38</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2">
         <v>155.38</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2">
         <v>155.38</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="N2">
         <v>155.38</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="O2">
         <v>155.38</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="P2">
         <v>150.75</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="Q2">
         <v>120.81</v>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="R2">
         <v>126.04</v>
       </c>
-      <c r="R2" s="5" t="n">
+      <c r="S2">
         <v>144.84</v>
       </c>
-      <c r="S2" s="5" t="n">
+      <c r="T2">
         <v>155.38</v>
       </c>
-      <c r="T2" s="5" t="n">
+      <c r="U2">
         <v>155.38</v>
       </c>
-      <c r="U2" s="5" t="n">
+      <c r="V2">
         <v>176.9</v>
       </c>
-      <c r="V2" s="5" t="n">
+      <c r="W2">
         <v>155.38</v>
       </c>
-      <c r="W2" s="5" t="n">
+      <c r="X2">
         <v>155.38</v>
       </c>
-      <c r="X2" s="5" t="n">
+      <c r="Y2">
         <v>155.38</v>
       </c>
-      <c r="Y2" s="5" t="n">
+      <c r="Z2">
         <v>133.4</v>
       </c>
-      <c r="Z2" s="5" t="n">
+      <c r="AA2">
         <v>155.38</v>
       </c>
-      <c r="AA2" s="5" t="n">
+      <c r="AB2">
         <v>155.38</v>
       </c>
-      <c r="AB2" s="5" t="n">
+      <c r="AC2">
         <v>155.38</v>
       </c>
-      <c r="AC2" s="5" t="n">
+      <c r="AD2">
         <v>155.38</v>
       </c>
-      <c r="AD2" s="5" t="n">
+      <c r="AE2">
         <v>155.38</v>
       </c>
-      <c r="AE2" s="5" t="n">
+      <c r="AF2">
         <v>155.38</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3">
         <v>9829</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F3">
         <v>212.71</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="G3">
         <v>203.46</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="H3">
         <v>263.32</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="I3">
         <v>219.26</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="J3">
         <v>161.85</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="K3">
         <v>263.32</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3">
         <v>263.32</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3">
         <v>263.32</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="N3">
         <v>263.32</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="O3">
         <v>263.32</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="P3">
         <v>255.49</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="Q3">
         <v>204.75</v>
       </c>
-      <c r="Q3" s="5" t="n">
+      <c r="R3">
         <v>213.61</v>
       </c>
-      <c r="R3" s="5" t="n">
+      <c r="S3">
         <v>245.47</v>
       </c>
-      <c r="S3" s="5" t="n">
+      <c r="T3">
         <v>263.32</v>
       </c>
-      <c r="T3" s="5" t="n">
+      <c r="U3">
         <v>263.32</v>
       </c>
-      <c r="U3" s="5" t="n">
+      <c r="V3">
         <v>299.8</v>
       </c>
-      <c r="V3" s="5" t="n">
+      <c r="W3">
         <v>263.32</v>
       </c>
-      <c r="W3" s="5" t="n">
+      <c r="X3">
         <v>263.32</v>
       </c>
-      <c r="X3" s="5" t="n">
+      <c r="Y3">
         <v>263.32</v>
       </c>
-      <c r="Y3" s="5" t="n">
+      <c r="Z3">
         <v>226.07</v>
       </c>
-      <c r="Z3" s="5" t="n">
+      <c r="AA3">
         <v>263.32</v>
       </c>
-      <c r="AA3" s="5" t="n">
+      <c r="AB3">
         <v>263.32</v>
       </c>
-      <c r="AB3" s="5" t="n">
+      <c r="AC3">
         <v>263.32</v>
       </c>
-      <c r="AC3" s="5" t="n">
+      <c r="AD3">
         <v>263.32</v>
       </c>
-      <c r="AD3" s="5" t="n">
+      <c r="AE3">
         <v>263.32</v>
       </c>
-      <c r="AE3" s="5" t="n">
+      <c r="AF3">
         <v>263.32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4">
         <v>9826</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F4">
         <v>323.82</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4">
         <v>309.74</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="H4">
         <v>400.87</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="I4">
         <v>333.8</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="J4">
         <v>246.39</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="K4">
         <v>400.87</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="L4">
         <v>400.87</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4">
         <v>400.87</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="N4">
         <v>400.87</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="O4">
         <v>400.87</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="P4">
         <v>388.94</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="Q4">
         <v>311.7</v>
       </c>
-      <c r="Q4" s="5" t="n">
+      <c r="R4">
         <v>325.19</v>
       </c>
-      <c r="R4" s="5" t="n">
+      <c r="S4">
         <v>373.69</v>
       </c>
-      <c r="S4" s="5" t="n">
+      <c r="T4">
         <v>400.87</v>
       </c>
-      <c r="T4" s="5" t="n">
+      <c r="U4">
         <v>400.87</v>
       </c>
-      <c r="U4" s="5" t="n">
+      <c r="V4">
         <v>456.4</v>
       </c>
-      <c r="V4" s="5" t="n">
+      <c r="W4">
         <v>400.87</v>
       </c>
-      <c r="W4" s="5" t="n">
+      <c r="X4">
         <v>400.87</v>
       </c>
-      <c r="X4" s="5" t="n">
+      <c r="Y4">
         <v>400.87</v>
       </c>
-      <c r="Y4" s="5" t="n">
+      <c r="Z4">
         <v>344.16</v>
       </c>
-      <c r="Z4" s="5" t="n">
+      <c r="AA4">
         <v>400.87</v>
       </c>
-      <c r="AA4" s="5" t="n">
+      <c r="AB4">
         <v>400.87</v>
       </c>
-      <c r="AB4" s="5" t="n">
+      <c r="AC4">
         <v>400.87</v>
       </c>
-      <c r="AC4" s="5" t="n">
+      <c r="AD4">
         <v>400.87</v>
       </c>
-      <c r="AD4" s="5" t="n">
+      <c r="AE4">
         <v>400.87</v>
       </c>
-      <c r="AE4" s="5" t="n">
+      <c r="AF4">
         <v>400.87</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5">
         <v>9827</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F5">
         <v>459.83</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="G5">
         <v>439.84</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="H5">
         <v>569.24</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="I5">
         <v>473.99</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="J5">
         <v>349.87</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5">
         <v>569.24</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5">
         <v>569.24</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5">
         <v>569.24</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="N5">
         <v>569.24</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="O5">
         <v>569.24</v>
       </c>
-      <c r="O5" s="5" t="n">
-        <v>552.3</v>
-      </c>
-      <c r="P5" s="5" t="n">
+      <c r="P5">
+        <v>552.29999999999995</v>
+      </c>
+      <c r="Q5">
         <v>442.61</v>
       </c>
-      <c r="Q5" s="5" t="n">
+      <c r="R5">
         <v>461.77</v>
       </c>
-      <c r="R5" s="5" t="n">
+      <c r="S5">
         <v>530.64</v>
       </c>
-      <c r="S5" s="5" t="n">
+      <c r="T5">
         <v>569.24</v>
       </c>
-      <c r="T5" s="5" t="n">
+      <c r="U5">
         <v>569.24</v>
       </c>
-      <c r="U5" s="5" t="n">
+      <c r="V5">
         <v>648.1</v>
       </c>
-      <c r="V5" s="5" t="n">
+      <c r="W5">
         <v>569.24</v>
       </c>
-      <c r="W5" s="5" t="n">
+      <c r="X5">
         <v>569.24</v>
       </c>
-      <c r="X5" s="5" t="n">
+      <c r="Y5">
         <v>569.24</v>
       </c>
-      <c r="Y5" s="5" t="n">
+      <c r="Z5">
         <v>488.71</v>
       </c>
-      <c r="Z5" s="5" t="n">
+      <c r="AA5">
         <v>569.24</v>
       </c>
-      <c r="AA5" s="5" t="n">
+      <c r="AB5">
         <v>569.24</v>
       </c>
-      <c r="AB5" s="5" t="n">
+      <c r="AC5">
         <v>569.24</v>
       </c>
-      <c r="AC5" s="5" t="n">
+      <c r="AD5">
         <v>569.24</v>
       </c>
-      <c r="AD5" s="5" t="n">
+      <c r="AE5">
         <v>569.24</v>
       </c>
-      <c r="AE5" s="5" t="n">
+      <c r="AF5">
         <v>569.24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6">
         <v>36377</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F6">
         <v>67.05</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6">
         <v>64.14</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="H6">
         <v>83.01</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="I6">
         <v>69.12</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="J6">
         <v>51.02</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6">
         <v>83.01</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="L6">
         <v>83.01</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="M6">
         <v>83.01</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="N6">
         <v>83.01</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="O6">
         <v>83.01</v>
       </c>
-      <c r="O6" s="5" t="n">
-        <v>80.54</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>64.54</v>
-      </c>
-      <c r="Q6" s="5" t="n">
+      <c r="P6">
+        <v>80.540000000000006</v>
+      </c>
+      <c r="Q6">
+        <v>64.540000000000006</v>
+      </c>
+      <c r="R6">
         <v>67.34</v>
       </c>
-      <c r="R6" s="5" t="n">
+      <c r="S6">
         <v>77.38</v>
       </c>
-      <c r="S6" s="5" t="n">
+      <c r="T6">
         <v>83.01</v>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="U6">
         <v>83.01</v>
       </c>
-      <c r="U6" s="5" t="n">
+      <c r="V6">
         <v>94.51</v>
       </c>
-      <c r="V6" s="5" t="n">
+      <c r="W6">
         <v>83.01</v>
       </c>
-      <c r="W6" s="5" t="n">
+      <c r="X6">
         <v>83.01</v>
       </c>
-      <c r="X6" s="5" t="n">
+      <c r="Y6">
         <v>83.01</v>
       </c>
-      <c r="Y6" s="5" t="n">
-        <v>71.26</v>
-      </c>
-      <c r="Z6" s="5" t="n">
+      <c r="Z6">
+        <v>71.260000000000005</v>
+      </c>
+      <c r="AA6">
         <v>83.01</v>
       </c>
-      <c r="AA6" s="5" t="n">
+      <c r="AB6">
         <v>83.01</v>
       </c>
-      <c r="AB6" s="5" t="n">
+      <c r="AC6">
         <v>83.01</v>
       </c>
-      <c r="AC6" s="5" t="n">
+      <c r="AD6">
         <v>83.01</v>
       </c>
-      <c r="AD6" s="5" t="n">
+      <c r="AE6">
         <v>83.01</v>
       </c>
-      <c r="AE6" s="5" t="n">
+      <c r="AF6">
         <v>83.01</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7">
         <v>36375</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F7">
         <v>20.43</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7">
         <v>19.55</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7">
         <v>25.3</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="I7">
         <v>21.06</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="J7">
         <v>15.55</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="K7">
         <v>25.3</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7">
         <v>25.3</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7">
         <v>25.3</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="N7">
         <v>25.3</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="O7">
         <v>25.3</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="P7">
         <v>24.54</v>
       </c>
-      <c r="P7" s="5" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="Q7" s="5" t="n">
+      <c r="Q7">
+        <v>19.670000000000002</v>
+      </c>
+      <c r="R7">
         <v>20.52</v>
       </c>
-      <c r="R7" s="5" t="n">
+      <c r="S7">
         <v>23.58</v>
       </c>
-      <c r="S7" s="5" t="n">
+      <c r="T7">
         <v>25.3</v>
       </c>
-      <c r="T7" s="5" t="n">
+      <c r="U7">
         <v>25.3</v>
       </c>
-      <c r="U7" s="5" t="n">
+      <c r="V7">
         <v>28.8</v>
       </c>
-      <c r="V7" s="5" t="n">
+      <c r="W7">
         <v>25.3</v>
       </c>
-      <c r="W7" s="5" t="n">
+      <c r="X7">
         <v>25.3</v>
       </c>
-      <c r="X7" s="5" t="n">
+      <c r="Y7">
         <v>25.3</v>
       </c>
-      <c r="Y7" s="5" t="n">
+      <c r="Z7">
         <v>21.72</v>
       </c>
-      <c r="Z7" s="5" t="n">
+      <c r="AA7">
         <v>25.3</v>
       </c>
-      <c r="AA7" s="5" t="n">
+      <c r="AB7">
         <v>25.3</v>
       </c>
-      <c r="AB7" s="5" t="n">
+      <c r="AC7">
         <v>25.3</v>
       </c>
-      <c r="AC7" s="5" t="n">
+      <c r="AD7">
         <v>25.3</v>
       </c>
-      <c r="AD7" s="5" t="n">
+      <c r="AE7">
         <v>25.3</v>
       </c>
-      <c r="AE7" s="5" t="n">
+      <c r="AF7">
         <v>25.3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8">
         <v>36376</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>40.13</v>
-      </c>
-      <c r="F8" s="5" t="n">
+      <c r="E8" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F8">
+        <v>40.130000000000003</v>
+      </c>
+      <c r="G8">
         <v>38.39</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="H8">
         <v>49.68</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="I8">
         <v>41.37</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="J8">
         <v>30.53</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="K8">
         <v>49.68</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="L8">
         <v>49.68</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8">
         <v>49.68</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="N8">
         <v>49.68</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="O8">
         <v>49.68</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="P8">
         <v>48.2</v>
       </c>
-      <c r="P8" s="5" t="n">
-        <v>38.63</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="R8" s="5" t="n">
+      <c r="Q8">
+        <v>38.630000000000003</v>
+      </c>
+      <c r="R8">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="S8">
         <v>46.31</v>
       </c>
-      <c r="S8" s="5" t="n">
+      <c r="T8">
         <v>49.68</v>
       </c>
-      <c r="T8" s="5" t="n">
+      <c r="U8">
         <v>49.68</v>
       </c>
-      <c r="U8" s="5" t="n">
+      <c r="V8">
         <v>56.56</v>
       </c>
-      <c r="V8" s="5" t="n">
+      <c r="W8">
         <v>49.68</v>
       </c>
-      <c r="W8" s="5" t="n">
+      <c r="X8">
         <v>49.68</v>
       </c>
-      <c r="X8" s="5" t="n">
+      <c r="Y8">
         <v>49.68</v>
       </c>
-      <c r="Y8" s="5" t="n">
+      <c r="Z8">
         <v>42.65</v>
       </c>
-      <c r="Z8" s="5" t="n">
+      <c r="AA8">
         <v>49.68</v>
       </c>
-      <c r="AA8" s="5" t="n">
+      <c r="AB8">
         <v>49.68</v>
       </c>
-      <c r="AB8" s="5" t="n">
+      <c r="AC8">
         <v>49.68</v>
       </c>
-      <c r="AC8" s="5" t="n">
+      <c r="AD8">
         <v>49.68</v>
       </c>
-      <c r="AD8" s="5" t="n">
+      <c r="AE8">
         <v>49.68</v>
       </c>
-      <c r="AE8" s="5" t="n">
+      <c r="AF8">
         <v>49.68</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9">
         <v>90694</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F9">
         <v>50.5</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9">
         <v>44.54</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="H9">
         <v>41.47</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>33.62</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9">
+        <v>33.619999999999997</v>
+      </c>
+      <c r="J9">
         <v>41.9</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="K9">
         <v>46.21</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="L9">
         <v>46.59</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="M9">
         <v>59.63</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="N9">
         <v>49.09</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="O9">
         <v>41.42</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="P9">
         <v>48.08</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="Q9">
         <v>49.54</v>
       </c>
-      <c r="Q9" s="5" t="n">
+      <c r="R9">
         <v>47.13</v>
       </c>
-      <c r="R9" s="5" t="n">
+      <c r="S9">
         <v>47.07</v>
       </c>
-      <c r="S9" s="5" t="n">
-        <v>40.66</v>
-      </c>
-      <c r="T9" s="5" t="n">
+      <c r="T9">
+        <v>40.659999999999997</v>
+      </c>
+      <c r="U9">
         <v>37.42</v>
       </c>
-      <c r="U9" s="5" t="n">
+      <c r="V9">
         <v>42.72</v>
       </c>
-      <c r="V9" s="5" t="n">
+      <c r="W9">
         <v>44.96</v>
       </c>
-      <c r="W9" s="5" t="n">
+      <c r="X9">
         <v>51.31</v>
       </c>
-      <c r="X9" s="5" t="n">
+      <c r="Y9">
         <v>46.03</v>
       </c>
-      <c r="Y9" s="5" t="n">
+      <c r="Z9">
         <v>54.02</v>
       </c>
-      <c r="Z9" s="5" t="n">
+      <c r="AA9">
         <v>40.33</v>
       </c>
-      <c r="AA9" s="5" t="n">
+      <c r="AB9">
         <v>50.57</v>
       </c>
-      <c r="AB9" s="5" t="n">
+      <c r="AC9">
         <v>45.53</v>
       </c>
-      <c r="AC9" s="5" t="n">
+      <c r="AD9">
         <v>43.5</v>
       </c>
-      <c r="AD9" s="5" t="n">
+      <c r="AE9">
         <v>50.71</v>
       </c>
-      <c r="AE9" s="5" t="n">
+      <c r="AF9">
         <v>45.18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10">
         <v>90695</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F10">
         <v>96.12</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10">
         <v>85.05</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>78.1</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="I10">
         <v>63.71</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="J10">
         <v>78.94</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10">
         <v>87.74</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10">
         <v>88.21</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10">
         <v>113.54</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="N10">
         <v>93.74</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="O10">
         <v>78.59</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="P10">
         <v>91.4</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="Q10">
         <v>94.65</v>
       </c>
-      <c r="Q10" s="5" t="n">
+      <c r="R10">
         <v>90.14</v>
       </c>
-      <c r="R10" s="5" t="n">
+      <c r="S10">
         <v>89.51</v>
       </c>
-      <c r="S10" s="5" t="n">
+      <c r="T10">
         <v>77.52</v>
       </c>
-      <c r="T10" s="5" t="n">
+      <c r="U10">
         <v>70.73</v>
       </c>
-      <c r="U10" s="5" t="n">
+      <c r="V10">
         <v>81.23</v>
       </c>
-      <c r="V10" s="5" t="n">
+      <c r="W10">
         <v>84.9</v>
       </c>
-      <c r="W10" s="5" t="n">
+      <c r="X10">
         <v>96.32</v>
       </c>
-      <c r="X10" s="5" t="n">
+      <c r="Y10">
         <v>87.36</v>
       </c>
-      <c r="Y10" s="5" t="n">
+      <c r="Z10">
         <v>103.05</v>
       </c>
-      <c r="Z10" s="5" t="n">
+      <c r="AA10">
         <v>76.38</v>
       </c>
-      <c r="AA10" s="5" t="n">
+      <c r="AB10">
         <v>96.21</v>
       </c>
-      <c r="AB10" s="5" t="n">
+      <c r="AC10">
         <v>86.61</v>
       </c>
-      <c r="AC10" s="5" t="n">
+      <c r="AD10">
         <v>82.72</v>
       </c>
-      <c r="AD10" s="5" t="n">
+      <c r="AE10">
         <v>95.67</v>
       </c>
-      <c r="AE10" s="5" t="n">
+      <c r="AF10">
         <v>86.18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11">
         <v>90696</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F11">
         <v>160.74</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11">
         <v>142.4</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="H11">
         <v>129.9</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="I11">
         <v>106.24</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>131.33</v>
-      </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11">
+        <v>131.33000000000001</v>
+      </c>
+      <c r="K11">
         <v>146.49</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="L11">
         <v>147.06</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="M11">
         <v>189.88</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="N11">
         <v>156.99</v>
       </c>
-      <c r="N11" s="5" t="n">
-        <v>131.17</v>
-      </c>
-      <c r="O11" s="5" t="n">
+      <c r="O11">
+        <v>131.16999999999999</v>
+      </c>
+      <c r="P11">
         <v>152.72</v>
       </c>
-      <c r="P11" s="5" t="n">
-        <v>158.55</v>
-      </c>
-      <c r="Q11" s="5" t="n">
+      <c r="Q11">
+        <v>158.55000000000001</v>
+      </c>
+      <c r="R11">
         <v>151.1</v>
       </c>
-      <c r="R11" s="5" t="n">
-        <v>149.61</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>129.73</v>
-      </c>
-      <c r="T11" s="5" t="n">
+      <c r="S11">
+        <v>149.61000000000001</v>
+      </c>
+      <c r="T11">
+        <v>129.72999999999999</v>
+      </c>
+      <c r="U11">
         <v>117.87</v>
       </c>
-      <c r="U11" s="5" t="n">
+      <c r="V11">
         <v>135.71</v>
       </c>
-      <c r="V11" s="5" t="n">
+      <c r="W11">
         <v>141.35</v>
       </c>
-      <c r="W11" s="5" t="n">
+      <c r="X11">
         <v>159.91</v>
       </c>
-      <c r="X11" s="5" t="n">
+      <c r="Y11">
         <v>145.88</v>
       </c>
-      <c r="Y11" s="5" t="n">
+      <c r="Z11">
         <v>172.51</v>
       </c>
-      <c r="Z11" s="5" t="n">
+      <c r="AA11">
         <v>127.39</v>
       </c>
-      <c r="AA11" s="5" t="n">
+      <c r="AB11">
         <v>160.85</v>
       </c>
-      <c r="AB11" s="5" t="n">
+      <c r="AC11">
         <v>144.75</v>
       </c>
-      <c r="AC11" s="5" t="n">
+      <c r="AD11">
         <v>138.24</v>
       </c>
-      <c r="AD11" s="5" t="n">
+      <c r="AE11">
         <v>159.24</v>
       </c>
-      <c r="AE11" s="5" t="n">
-        <v>144.27</v>
+      <c r="AF11">
+        <v>144.27000000000001</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12">
         <v>90697</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F12">
         <v>249.52</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12">
         <v>221.26</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12">
         <v>200.97</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="I12">
         <v>164.67</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="J12">
         <v>203.2</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12">
         <v>227.21</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="L12">
         <v>227.9</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12">
         <v>294.77</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="N12">
         <v>243.92</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="O12">
         <v>203.39</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="P12">
         <v>236.97</v>
       </c>
-      <c r="P12" s="5" t="n">
+      <c r="Q12">
         <v>246.38</v>
       </c>
-      <c r="Q12" s="5" t="n">
+      <c r="R12">
         <v>234.88</v>
       </c>
-      <c r="R12" s="5" t="n">
+      <c r="S12">
         <v>232.17</v>
       </c>
-      <c r="S12" s="5" t="n">
+      <c r="T12">
         <v>201.46</v>
       </c>
-      <c r="T12" s="5" t="n">
+      <c r="U12">
         <v>182.56</v>
       </c>
-      <c r="U12" s="5" t="n">
+      <c r="V12">
         <v>210.6</v>
       </c>
-      <c r="V12" s="5" t="n">
+      <c r="W12">
         <v>218.86</v>
       </c>
-      <c r="W12" s="5" t="n">
+      <c r="X12">
         <v>247.16</v>
       </c>
-      <c r="X12" s="5" t="n">
+      <c r="Y12">
         <v>226.27</v>
       </c>
-      <c r="Y12" s="5" t="n">
+      <c r="Z12">
         <v>267.94</v>
       </c>
-      <c r="Z12" s="5" t="n">
+      <c r="AA12">
         <v>197.44</v>
       </c>
-      <c r="AA12" s="5" t="n">
+      <c r="AB12">
         <v>249.65</v>
       </c>
-      <c r="AB12" s="5" t="n">
+      <c r="AC12">
         <v>224.64</v>
       </c>
-      <c r="AC12" s="5" t="n">
+      <c r="AD12">
         <v>214.49</v>
       </c>
-      <c r="AD12" s="5" t="n">
+      <c r="AE12">
         <v>246.51</v>
       </c>
-      <c r="AE12" s="5" t="n">
+      <c r="AF12">
         <v>224.06</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13">
         <v>90698</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F13">
         <v>381.54</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13">
         <v>338.58</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13">
         <v>306.56</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="I13">
         <v>251.51</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="J13">
         <v>310</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="K13">
         <v>347.21</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="L13">
         <v>348.06</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13">
         <v>450.78</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="N13">
         <v>373.23</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="O13">
         <v>310.75</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="P13">
         <v>362.23</v>
       </c>
-      <c r="P13" s="5" t="n">
+      <c r="Q13">
         <v>377.04</v>
       </c>
-      <c r="Q13" s="5" t="n">
+      <c r="R13">
         <v>359.51</v>
       </c>
-      <c r="R13" s="5" t="n">
+      <c r="S13">
         <v>354.94</v>
       </c>
-      <c r="S13" s="5" t="n">
+      <c r="T13">
         <v>308.17</v>
       </c>
-      <c r="T13" s="5" t="n">
-        <v>278.71</v>
-      </c>
-      <c r="U13" s="5" t="n">
+      <c r="U13">
+        <v>278.70999999999998</v>
+      </c>
+      <c r="V13">
         <v>321.93</v>
       </c>
-      <c r="V13" s="5" t="n">
+      <c r="W13">
         <v>334.03</v>
       </c>
-      <c r="W13" s="5" t="n">
+      <c r="X13">
         <v>376.74</v>
       </c>
-      <c r="X13" s="5" t="n">
+      <c r="Y13">
         <v>345.78</v>
       </c>
-      <c r="Y13" s="5" t="n">
+      <c r="Z13">
         <v>409.92</v>
       </c>
-      <c r="Z13" s="5" t="n">
+      <c r="AA13">
         <v>301.56</v>
       </c>
-      <c r="AA13" s="5" t="n">
+      <c r="AB13">
         <v>381.69</v>
       </c>
-      <c r="AB13" s="5" t="n">
+      <c r="AC13">
         <v>343.42</v>
       </c>
-      <c r="AC13" s="5" t="n">
+      <c r="AD13">
         <v>327.9</v>
       </c>
-      <c r="AD13" s="5" t="n">
+      <c r="AE13">
         <v>376.17</v>
       </c>
-      <c r="AE13" s="5" t="n">
+      <c r="AF13">
         <v>342.76</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14">
         <v>90699</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F14">
         <v>537.15</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14">
         <v>476.83</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14">
         <v>430.97</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="I14">
         <v>353.83</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="J14">
         <v>435.82</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="K14">
         <v>488.62</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="L14">
         <v>489.64</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14">
         <v>634.65</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="N14">
         <v>525.62</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="O14">
         <v>437.3</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="P14">
         <v>509.84</v>
       </c>
-      <c r="P14" s="5" t="n">
-        <v>531.05</v>
-      </c>
-      <c r="Q14" s="5" t="n">
+      <c r="Q14">
+        <v>531.04999999999995</v>
+      </c>
+      <c r="R14">
         <v>506.43</v>
       </c>
-      <c r="R14" s="5" t="n">
+      <c r="S14">
         <v>499.63</v>
       </c>
-      <c r="S14" s="5" t="n">
+      <c r="T14">
         <v>433.93</v>
       </c>
-      <c r="T14" s="5" t="n">
+      <c r="U14">
         <v>392.02</v>
       </c>
-      <c r="U14" s="5" t="n">
+      <c r="V14">
         <v>453.15</v>
       </c>
-      <c r="V14" s="5" t="n">
+      <c r="W14">
         <v>469.73</v>
       </c>
-      <c r="W14" s="5" t="n">
+      <c r="X14">
         <v>529.37</v>
       </c>
-      <c r="X14" s="5" t="n">
+      <c r="Y14">
         <v>486.63</v>
       </c>
-      <c r="Y14" s="5" t="n">
+      <c r="Z14">
         <v>577.23</v>
       </c>
-      <c r="Z14" s="5" t="n">
+      <c r="AA14">
         <v>424.26</v>
       </c>
-      <c r="AA14" s="5" t="n">
-        <v>537.32</v>
-      </c>
-      <c r="AB14" s="5" t="n">
+      <c r="AB14">
+        <v>537.32000000000005</v>
+      </c>
+      <c r="AC14">
         <v>483.39</v>
       </c>
-      <c r="AC14" s="5" t="n">
+      <c r="AD14">
         <v>461.55</v>
       </c>
-      <c r="AD14" s="5" t="n">
+      <c r="AE14">
         <v>528.97</v>
       </c>
-      <c r="AE14" s="5" t="n">
+      <c r="AF14">
         <v>482.66</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15">
         <v>90700</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F15">
         <v>627.76</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15">
         <v>557.28</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15">
         <v>503.79</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="I15">
         <v>414.44</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="J15">
         <v>509.34</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="K15">
         <v>570.74</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L15">
         <v>571.38</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15">
         <v>740.25</v>
       </c>
-      <c r="M15" s="5" t="n">
-        <v>614.07</v>
-      </c>
-      <c r="N15" s="5" t="n">
+      <c r="N15">
+        <v>614.07000000000005</v>
+      </c>
+      <c r="O15">
         <v>510.92</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="P15">
         <v>595.71</v>
       </c>
-      <c r="P15" s="5" t="n">
+      <c r="Q15">
         <v>620.54</v>
       </c>
-      <c r="Q15" s="5" t="n">
-        <v>591.92</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>583.68</v>
-      </c>
-      <c r="S15" s="5" t="n">
+      <c r="R15">
+        <v>591.91999999999996</v>
+      </c>
+      <c r="S15">
+        <v>583.67999999999995</v>
+      </c>
+      <c r="T15">
         <v>507.32</v>
       </c>
-      <c r="T15" s="5" t="n">
+      <c r="U15">
         <v>458.16</v>
       </c>
-      <c r="U15" s="5" t="n">
+      <c r="V15">
         <v>529.6</v>
       </c>
-      <c r="V15" s="5" t="n">
+      <c r="W15">
         <v>548.27</v>
       </c>
-      <c r="W15" s="5" t="n">
-        <v>616.69</v>
-      </c>
-      <c r="X15" s="5" t="n">
+      <c r="X15">
+        <v>616.69000000000005</v>
+      </c>
+      <c r="Y15">
         <v>568.52</v>
       </c>
-      <c r="Y15" s="5" t="n">
+      <c r="Z15">
         <v>673.92</v>
       </c>
-      <c r="Z15" s="5" t="n">
+      <c r="AA15">
         <v>496.16</v>
       </c>
-      <c r="AA15" s="5" t="n">
+      <c r="AB15">
         <v>627.61</v>
       </c>
-      <c r="AB15" s="5" t="n">
+      <c r="AC15">
         <v>564.96</v>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>539.44</v>
-      </c>
-      <c r="AD15" s="5" t="n">
+      <c r="AD15">
+        <v>539.44000000000005</v>
+      </c>
+      <c r="AE15">
         <v>616.96</v>
       </c>
-      <c r="AE15" s="5" t="n">
-        <v>564.17</v>
+      <c r="AF15">
+        <v>564.16999999999996</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16">
         <v>97134</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="F16" s="5" t="n">
+      <c r="E16" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F16">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="G16">
         <v>3.49</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16">
         <v>4.8</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="I16">
         <v>3.42</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="J16">
         <v>4.82</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="K16">
         <v>4.37</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="L16">
         <v>4.76</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16">
         <v>5.12</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="N16">
         <v>3.86</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="O16">
         <v>4</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="P16">
         <v>4.38</v>
       </c>
-      <c r="P16" s="5" t="n">
+      <c r="Q16">
         <v>3.83</v>
       </c>
-      <c r="Q16" s="5" t="n">
+      <c r="R16">
         <v>3.51</v>
       </c>
-      <c r="R16" s="5" t="n">
+      <c r="S16">
         <v>4.22</v>
       </c>
-      <c r="S16" s="5" t="n">
+      <c r="T16">
         <v>3.36</v>
       </c>
-      <c r="T16" s="5" t="n">
+      <c r="U16">
         <v>3.98</v>
       </c>
-      <c r="U16" s="5" t="n">
+      <c r="V16">
         <v>3.88</v>
       </c>
-      <c r="V16" s="5" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="W16" s="5" t="n">
+      <c r="W16">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="X16">
         <v>6.4</v>
       </c>
-      <c r="X16" s="5" t="n">
+      <c r="Y16">
         <v>4.33</v>
       </c>
-      <c r="Y16" s="5" t="n">
+      <c r="Z16">
         <v>4.38</v>
       </c>
-      <c r="Z16" s="5" t="n">
+      <c r="AA16">
         <v>4.07</v>
       </c>
-      <c r="AA16" s="5" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="AB16" s="5" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AC16" s="5" t="n">
+      <c r="AB16">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="AC16">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="AD16">
         <v>3.93</v>
       </c>
-      <c r="AD16" s="5" t="n">
+      <c r="AE16">
         <v>5.62</v>
       </c>
-      <c r="AE16" s="5" t="n">
+      <c r="AF16">
         <v>3.7</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17">
         <v>97135</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>8.13</v>
-      </c>
-      <c r="F17" s="5" t="n">
+      <c r="E17" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F17">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="G17">
         <v>6.56</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17">
         <v>8.83</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="I17">
         <v>6.6</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="J17">
         <v>8.82</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="K17">
         <v>7.95</v>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="M17">
         <v>8.94</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="N17">
         <v>7.18</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="O17">
         <v>7.29</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="P17">
         <v>8.11</v>
       </c>
-      <c r="P17" s="5" t="n">
+      <c r="Q17">
         <v>7.19</v>
       </c>
-      <c r="Q17" s="5" t="n">
+      <c r="R17">
         <v>6.62</v>
       </c>
-      <c r="R17" s="5" t="n">
+      <c r="S17">
         <v>7.71</v>
       </c>
-      <c r="S17" s="5" t="n">
+      <c r="T17">
         <v>6.38</v>
       </c>
-      <c r="T17" s="5" t="n">
+      <c r="U17">
         <v>7.23</v>
       </c>
-      <c r="U17" s="5" t="n">
+      <c r="V17">
         <v>7.18</v>
       </c>
-      <c r="V17" s="5" t="n">
+      <c r="W17">
         <v>8.68</v>
       </c>
-      <c r="W17" s="5" t="n">
+      <c r="X17">
         <v>10.68</v>
       </c>
-      <c r="X17" s="5" t="n">
+      <c r="Y17">
         <v>7.96</v>
       </c>
-      <c r="Y17" s="5" t="n">
+      <c r="Z17">
         <v>7.92</v>
       </c>
-      <c r="Z17" s="5" t="n">
+      <c r="AA17">
         <v>7.59</v>
       </c>
-      <c r="AA17" s="5" t="n">
+      <c r="AB17">
         <v>8.19</v>
       </c>
-      <c r="AB17" s="5" t="n">
+      <c r="AC17">
         <v>7.61</v>
       </c>
-      <c r="AC17" s="5" t="n">
+      <c r="AD17">
         <v>7.3</v>
       </c>
-      <c r="AD17" s="5" t="n">
+      <c r="AE17">
         <v>9.77</v>
       </c>
-      <c r="AE17" s="5" t="n">
+      <c r="AF17">
         <v>6.96</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18">
         <v>97136</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F18">
         <v>9.64</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18">
         <v>7.79</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18">
         <v>10.46</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="I18">
         <v>7.81</v>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="J18">
         <v>10.44</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="K18">
         <v>9.42</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="L18">
         <v>9.85</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18">
         <v>10.61</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="N18">
         <v>8.51</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="O18">
         <v>8.64</v>
       </c>
-      <c r="O18" s="5" t="n">
+      <c r="P18">
         <v>9.6</v>
       </c>
-      <c r="P18" s="5" t="n">
+      <c r="Q18">
         <v>8.52</v>
       </c>
-      <c r="Q18" s="5" t="n">
+      <c r="R18">
         <v>7.85</v>
       </c>
-      <c r="R18" s="5" t="n">
+      <c r="S18">
         <v>9.15</v>
       </c>
-      <c r="S18" s="5" t="n">
+      <c r="T18">
         <v>7.56</v>
       </c>
-      <c r="T18" s="5" t="n">
+      <c r="U18">
         <v>8.57</v>
       </c>
-      <c r="U18" s="5" t="n">
+      <c r="V18">
         <v>8.51</v>
       </c>
-      <c r="V18" s="5" t="n">
+      <c r="W18">
         <v>10.28</v>
       </c>
-      <c r="W18" s="5" t="n">
+      <c r="X18">
         <v>12.65</v>
       </c>
-      <c r="X18" s="5" t="n">
+      <c r="Y18">
         <v>9.44</v>
       </c>
-      <c r="Y18" s="5" t="n">
+      <c r="Z18">
         <v>9.39</v>
       </c>
-      <c r="Z18" s="5" t="n">
+      <c r="AA18">
         <v>8.99</v>
       </c>
-      <c r="AA18" s="5" t="n">
-        <v>9.72</v>
-      </c>
-      <c r="AB18" s="5" t="n">
+      <c r="AB18">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="AC18">
         <v>9.02</v>
       </c>
-      <c r="AC18" s="5" t="n">
+      <c r="AD18">
         <v>8.66</v>
       </c>
-      <c r="AD18" s="5" t="n">
+      <c r="AE18">
         <v>11.57</v>
       </c>
-      <c r="AE18" s="5" t="n">
+      <c r="AF18">
         <v>8.24</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19">
         <v>97137</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F19">
         <v>11.17</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19">
         <v>9.01</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="H19">
         <v>12.09</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="I19">
         <v>9.06</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="J19">
         <v>12.07</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="K19">
         <v>10.89</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="L19">
         <v>11.39</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19">
         <v>12.26</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="N19">
         <v>9.85</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="O19">
         <v>9.99</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="P19">
         <v>11.12</v>
       </c>
-      <c r="P19" s="5" t="n">
-        <v>9.88</v>
-      </c>
-      <c r="Q19" s="5" t="n">
+      <c r="Q19">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="R19">
         <v>9.08</v>
       </c>
-      <c r="R19" s="5" t="n">
+      <c r="S19">
         <v>10.6</v>
       </c>
-      <c r="S19" s="5" t="n">
+      <c r="T19">
         <v>8.75</v>
       </c>
-      <c r="T19" s="5" t="n">
+      <c r="U19">
         <v>9.93</v>
       </c>
-      <c r="U19" s="5" t="n">
+      <c r="V19">
         <v>9.85</v>
       </c>
-      <c r="V19" s="5" t="n">
+      <c r="W19">
         <v>11.92</v>
       </c>
-      <c r="W19" s="5" t="n">
+      <c r="X19">
         <v>14.64</v>
       </c>
-      <c r="X19" s="5" t="n">
+      <c r="Y19">
         <v>10.92</v>
       </c>
-      <c r="Y19" s="5" t="n">
+      <c r="Z19">
         <v>10.85</v>
       </c>
-      <c r="Z19" s="5" t="n">
+      <c r="AA19">
         <v>10.41</v>
       </c>
-      <c r="AA19" s="5" t="n">
+      <c r="AB19">
         <v>11.24</v>
       </c>
-      <c r="AB19" s="5" t="n">
+      <c r="AC19">
         <v>10.44</v>
       </c>
-      <c r="AC19" s="5" t="n">
+      <c r="AD19">
         <v>10.01</v>
       </c>
-      <c r="AD19" s="5" t="n">
+      <c r="AE19">
         <v>13.38</v>
       </c>
-      <c r="AE19" s="5" t="n">
+      <c r="AF19">
         <v>9.56</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20">
         <v>97126</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F20">
         <v>3.59</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20">
         <v>2.86</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="H20">
         <v>3.97</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="I20">
         <v>2.78</v>
       </c>
-      <c r="I20" s="5" t="n">
+      <c r="J20">
         <v>3.97</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20">
         <v>3.59</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20">
         <v>3.91</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20">
         <v>4.21</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="N20">
         <v>3.16</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="O20">
         <v>3.28</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="P20">
         <v>3.59</v>
       </c>
-      <c r="P20" s="5" t="n">
+      <c r="Q20">
         <v>3.13</v>
       </c>
-      <c r="Q20" s="5" t="n">
+      <c r="R20">
         <v>2.85</v>
       </c>
-      <c r="R20" s="5" t="n">
+      <c r="S20">
         <v>3.46</v>
       </c>
-      <c r="S20" s="5" t="n">
+      <c r="T20">
         <v>2.76</v>
       </c>
-      <c r="T20" s="5" t="n">
+      <c r="U20">
         <v>3.27</v>
       </c>
-      <c r="U20" s="5" t="n">
+      <c r="V20">
         <v>3.17</v>
       </c>
-      <c r="V20" s="5" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="W20" s="5" t="n">
+      <c r="W20">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="X20">
         <v>5.29</v>
       </c>
-      <c r="X20" s="5" t="n">
+      <c r="Y20">
         <v>3.56</v>
       </c>
-      <c r="Y20" s="5" t="n">
+      <c r="Z20">
         <v>3.59</v>
       </c>
-      <c r="Z20" s="5" t="n">
+      <c r="AA20">
         <v>3.34</v>
       </c>
-      <c r="AA20" s="5" t="n">
+      <c r="AB20">
         <v>3.66</v>
       </c>
-      <c r="AB20" s="5" t="n">
+      <c r="AC20">
         <v>3.35</v>
       </c>
-      <c r="AC20" s="5" t="n">
+      <c r="AD20">
         <v>3.22</v>
       </c>
-      <c r="AD20" s="5" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE20" s="5" t="n">
+      <c r="AE20">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="AF20">
         <v>3.02</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21">
         <v>97124</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="F21" s="5" t="n">
+      <c r="E21" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F21">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="G21">
         <v>2.04</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="H21">
         <v>2.85</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="I21">
         <v>1.97</v>
       </c>
-      <c r="I21" s="5" t="n">
+      <c r="J21">
         <v>2.84</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="K21">
         <v>2.56</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="L21">
         <v>2.78</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21">
         <v>3</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="N21">
         <v>2.23</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="O21">
         <v>2.34</v>
       </c>
-      <c r="O21" s="5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P21" s="5" t="n">
+      <c r="P21">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Q21">
         <v>2.21</v>
       </c>
-      <c r="Q21" s="5" t="n">
+      <c r="R21">
         <v>2</v>
       </c>
-      <c r="R21" s="5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="S21" s="5" t="n">
+      <c r="S21">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="T21">
         <v>1.97</v>
       </c>
-      <c r="T21" s="5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U21" s="5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V21" s="5" t="n">
+      <c r="U21">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="V21">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="W21">
         <v>2.9</v>
       </c>
-      <c r="W21" s="5" t="n">
+      <c r="X21">
         <v>3.8</v>
       </c>
-      <c r="X21" s="5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y21" s="5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z21" s="5" t="n">
+      <c r="Y21">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Z21">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AA21">
         <v>2.38</v>
       </c>
-      <c r="AA21" s="5" t="n">
+      <c r="AB21">
         <v>2.59</v>
       </c>
-      <c r="AB21" s="5" t="n">
+      <c r="AC21">
         <v>2.36</v>
       </c>
-      <c r="AC21" s="5" t="n">
+      <c r="AD21">
         <v>2.29</v>
       </c>
-      <c r="AD21" s="5" t="n">
+      <c r="AE21">
         <v>3.34</v>
       </c>
-      <c r="AE21" s="5" t="n">
+      <c r="AF21">
         <v>2.15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22">
         <v>97125</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F22">
         <v>3.09</v>
       </c>
-      <c r="F22" s="5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="H22">
         <v>3.42</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="I22">
         <v>2.38</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="J22">
         <v>3.42</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="K22">
         <v>3.08</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="L22">
         <v>3.36</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="M22">
         <v>3.61</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="N22">
         <v>2.71</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="O22">
         <v>2.83</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="P22">
         <v>3.08</v>
       </c>
-      <c r="P22" s="5" t="n">
+      <c r="Q22">
         <v>2.68</v>
       </c>
-      <c r="Q22" s="5" t="n">
+      <c r="R22">
         <v>2.44</v>
       </c>
-      <c r="R22" s="5" t="n">
+      <c r="S22">
         <v>2.97</v>
       </c>
-      <c r="S22" s="5" t="n">
+      <c r="T22">
         <v>2.38</v>
       </c>
-      <c r="T22" s="5" t="n">
+      <c r="U22">
         <v>2.8</v>
       </c>
-      <c r="U22" s="5" t="n">
+      <c r="V22">
         <v>2.73</v>
       </c>
-      <c r="V22" s="5" t="n">
+      <c r="W22">
         <v>3.49</v>
       </c>
-      <c r="W22" s="5" t="n">
+      <c r="X22">
         <v>4.55</v>
       </c>
-      <c r="X22" s="5" t="n">
+      <c r="Y22">
         <v>3.06</v>
       </c>
-      <c r="Y22" s="5" t="n">
+      <c r="Z22">
         <v>3.09</v>
       </c>
-      <c r="Z22" s="5" t="n">
+      <c r="AA22">
         <v>2.87</v>
       </c>
-      <c r="AA22" s="5" t="n">
+      <c r="AB22">
         <v>3.14</v>
       </c>
-      <c r="AB22" s="5" t="n">
+      <c r="AC22">
         <v>2.88</v>
       </c>
-      <c r="AC22" s="5" t="n">
+      <c r="AD22">
         <v>2.77</v>
       </c>
-      <c r="AD22" s="5" t="n">
+      <c r="AE22">
         <v>4.01</v>
       </c>
-      <c r="AE22" s="5" t="n">
+      <c r="AF22">
         <v>2.6</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23">
         <v>93382</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F23">
         <v>30.26</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23">
         <v>24.78</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23">
         <v>32.97</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="I23">
         <v>26.41</v>
       </c>
-      <c r="I23" s="5" t="n">
+      <c r="J23">
         <v>30.57</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="K23">
         <v>29.04</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="L23">
         <v>28.49</v>
       </c>
-      <c r="L23" s="5" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="M23" s="5" t="n">
+      <c r="M23">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="N23">
         <v>25.76</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="O23">
         <v>28.11</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="P23">
         <v>28.46</v>
       </c>
-      <c r="P23" s="5" t="n">
+      <c r="Q23">
         <v>26.05</v>
       </c>
-      <c r="Q23" s="5" t="n">
+      <c r="R23">
         <v>24.62</v>
       </c>
-      <c r="R23" s="5" t="n">
+      <c r="S23">
         <v>29.16</v>
       </c>
-      <c r="S23" s="5" t="n">
+      <c r="T23">
         <v>23.96</v>
       </c>
-      <c r="T23" s="5" t="n">
+      <c r="U23">
         <v>27.41</v>
       </c>
-      <c r="U23" s="5" t="n">
+      <c r="V23">
         <v>25.75</v>
       </c>
-      <c r="V23" s="5" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="W23" s="5" t="n">
+      <c r="W23">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="X23">
         <v>37.43</v>
       </c>
-      <c r="X23" s="5" t="n">
+      <c r="Y23">
         <v>27.2</v>
       </c>
-      <c r="Y23" s="5" t="n">
+      <c r="Z23">
         <v>32.17</v>
       </c>
-      <c r="Z23" s="5" t="n">
+      <c r="AA23">
         <v>28.43</v>
       </c>
-      <c r="AA23" s="5" t="n">
+      <c r="AB23">
         <v>30.98</v>
       </c>
-      <c r="AB23" s="5" t="n">
+      <c r="AC23">
         <v>29.56</v>
       </c>
-      <c r="AC23" s="5" t="n">
+      <c r="AD23">
         <v>26.69</v>
       </c>
-      <c r="AD23" s="5" t="n">
+      <c r="AE23">
         <v>35.28</v>
       </c>
-      <c r="AE23" s="5" t="n">
+      <c r="AF23">
         <v>25.95</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24">
         <v>93380</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="F24" s="5" t="n">
+      <c r="E24" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F24">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="G24">
         <v>14.18</v>
       </c>
-      <c r="G24" s="5" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24">
+        <v>19.440000000000001</v>
+      </c>
+      <c r="I24">
         <v>16.52</v>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="J24">
         <v>18.5</v>
       </c>
-      <c r="J24" s="5" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="K24" s="5" t="n">
+      <c r="K24">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="L24">
         <v>15.5</v>
       </c>
-      <c r="L24" s="5" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="M24" s="5" t="n">
+      <c r="M24">
+        <v>17.760000000000002</v>
+      </c>
+      <c r="N24">
         <v>14.76</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="O24">
         <v>15.53</v>
       </c>
-      <c r="O24" s="5" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="P24" s="5" t="n">
+      <c r="P24">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="Q24">
         <v>15.45</v>
       </c>
-      <c r="Q24" s="5" t="n">
+      <c r="R24">
         <v>14.27</v>
       </c>
-      <c r="R24" s="5" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="S24" s="5" t="n">
+      <c r="S24">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="T24">
         <v>14.07</v>
       </c>
-      <c r="T24" s="5" t="n">
+      <c r="U24">
         <v>14.8</v>
       </c>
-      <c r="U24" s="5" t="n">
+      <c r="V24">
         <v>15.07</v>
       </c>
-      <c r="V24" s="5" t="n">
+      <c r="W24">
         <v>17.5</v>
       </c>
-      <c r="W24" s="5" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="X24" s="5" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="Y24" s="5" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="Z24" s="5" t="n">
+      <c r="X24">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="Y24">
+        <v>16.309999999999999</v>
+      </c>
+      <c r="Z24">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="AA24">
         <v>16.89</v>
       </c>
-      <c r="AA24" s="5" t="n">
+      <c r="AB24">
         <v>18.23</v>
       </c>
-      <c r="AB24" s="5" t="n">
-        <v>16.69</v>
-      </c>
-      <c r="AC24" s="5" t="n">
+      <c r="AC24">
+        <v>16.690000000000001</v>
+      </c>
+      <c r="AD24">
         <v>15.96</v>
       </c>
-      <c r="AD24" s="5" t="n">
+      <c r="AE24">
         <v>18.48</v>
       </c>
-      <c r="AE24" s="5" t="n">
+      <c r="AF24">
         <v>15.34</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25">
         <v>93378</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F25">
         <v>27.46</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="G25">
         <v>21.68</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="H25">
         <v>29.59</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="I25">
         <v>24.98</v>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="J25">
         <v>28.28</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="K25">
         <v>25.86</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="L25">
         <v>23.7</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="M25">
         <v>27.04</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="N25">
         <v>22.62</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="O25">
         <v>23.66</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="P25">
         <v>26.56</v>
       </c>
-      <c r="P25" s="5" t="n">
+      <c r="Q25">
         <v>23.62</v>
       </c>
-      <c r="Q25" s="5" t="n">
+      <c r="R25">
         <v>21.78</v>
       </c>
-      <c r="R25" s="5" t="n">
+      <c r="S25">
         <v>24.66</v>
       </c>
-      <c r="S25" s="5" t="n">
+      <c r="T25">
         <v>21.5</v>
       </c>
-      <c r="T25" s="5" t="n">
+      <c r="U25">
         <v>22.62</v>
       </c>
-      <c r="U25" s="5" t="n">
+      <c r="V25">
         <v>23.04</v>
       </c>
-      <c r="V25" s="5" t="n">
+      <c r="W25">
         <v>26.67</v>
       </c>
-      <c r="W25" s="5" t="n">
+      <c r="X25">
         <v>29.43</v>
       </c>
-      <c r="X25" s="5" t="n">
+      <c r="Y25">
         <v>24.99</v>
       </c>
-      <c r="Y25" s="5" t="n">
+      <c r="Z25">
         <v>26.36</v>
       </c>
-      <c r="Z25" s="5" t="n">
+      <c r="AA25">
         <v>25.71</v>
       </c>
-      <c r="AA25" s="5" t="n">
+      <c r="AB25">
         <v>27.67</v>
       </c>
-      <c r="AB25" s="5" t="n">
+      <c r="AC25">
         <v>25.44</v>
       </c>
-      <c r="AC25" s="5" t="n">
+      <c r="AD25">
         <v>24.31</v>
       </c>
-      <c r="AD25" s="5" t="n">
+      <c r="AE25">
         <v>28.3</v>
       </c>
-      <c r="AE25" s="5" t="n">
+      <c r="AF25">
         <v>23.32</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26">
         <v>98114</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F26">
         <v>620.86</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>602.32</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>618.33</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>607.67</v>
-      </c>
-      <c r="I26" s="5" t="n">
+      <c r="G26">
+        <v>602.32000000000005</v>
+      </c>
+      <c r="H26">
+        <v>618.33000000000004</v>
+      </c>
+      <c r="I26">
+        <v>607.66999999999996</v>
+      </c>
+      <c r="J26">
         <v>801.76</v>
       </c>
-      <c r="J26" s="5" t="n">
-        <v>609.44</v>
-      </c>
-      <c r="K26" s="5" t="n">
+      <c r="K26">
+        <v>609.44000000000005</v>
+      </c>
+      <c r="L26">
         <v>615.86</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="M26">
         <v>614.76</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="N26">
         <v>610.49</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="O26">
         <v>611.15</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="P26">
         <v>528.48</v>
       </c>
-      <c r="P26" s="5" t="n">
+      <c r="Q26">
         <v>603.46</v>
       </c>
-      <c r="Q26" s="5" t="n">
-        <v>604.7</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>617.18</v>
-      </c>
-      <c r="S26" s="5" t="n">
+      <c r="R26">
+        <v>604.70000000000005</v>
+      </c>
+      <c r="S26">
+        <v>617.17999999999995</v>
+      </c>
+      <c r="T26">
         <v>599.79</v>
       </c>
-      <c r="T26" s="5" t="n">
-        <v>608.8</v>
-      </c>
-      <c r="U26" s="5" t="n">
+      <c r="U26">
+        <v>608.79999999999995</v>
+      </c>
+      <c r="V26">
         <v>607.72</v>
       </c>
-      <c r="V26" s="5" t="n">
+      <c r="W26">
         <v>854.52</v>
       </c>
-      <c r="W26" s="5" t="n">
+      <c r="X26">
         <v>628.75</v>
       </c>
-      <c r="X26" s="5" t="n">
+      <c r="Y26">
         <v>604.38</v>
       </c>
-      <c r="Y26" s="5" t="n">
-        <v>619.55</v>
-      </c>
-      <c r="Z26" s="5" t="n">
+      <c r="Z26">
+        <v>619.54999999999995</v>
+      </c>
+      <c r="AA26">
         <v>622.4</v>
       </c>
-      <c r="AA26" s="5" t="n">
+      <c r="AB26">
         <v>609.96</v>
       </c>
-      <c r="AB26" s="5" t="n">
+      <c r="AC26">
         <v>618.04</v>
       </c>
-      <c r="AC26" s="5" t="n">
+      <c r="AD26">
         <v>604.39</v>
       </c>
-      <c r="AD26" s="5" t="n">
-        <v>619.82</v>
-      </c>
-      <c r="AE26" s="5" t="n">
+      <c r="AE26">
+        <v>619.82000000000005</v>
+      </c>
+      <c r="AF26">
         <v>606.89</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27">
         <v>90099</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="E27" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F27">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="G27">
         <v>14.35</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="H27">
         <v>17.93</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="I27">
         <v>14.75</v>
       </c>
-      <c r="I27" s="5" t="n">
-        <v>17.44</v>
-      </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27">
+        <v>17.440000000000001</v>
+      </c>
+      <c r="K27">
         <v>15.99</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="L27">
         <v>15.58</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="M27">
         <v>16.64</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="N27">
         <v>15.14</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="O27">
         <v>15.04</v>
       </c>
-      <c r="O27" s="5" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="P27" s="5" t="n">
+      <c r="P27">
+        <v>16.440000000000001</v>
+      </c>
+      <c r="Q27">
         <v>15.25</v>
       </c>
-      <c r="Q27" s="5" t="n">
+      <c r="R27">
         <v>14.46</v>
       </c>
-      <c r="R27" s="5" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="S27" s="5" t="n">
+      <c r="S27">
+        <v>16.010000000000002</v>
+      </c>
+      <c r="T27">
         <v>14.07</v>
       </c>
-      <c r="T27" s="5" t="n">
+      <c r="U27">
         <v>14.89</v>
       </c>
-      <c r="U27" s="5" t="n">
+      <c r="V27">
         <v>14.97</v>
       </c>
-      <c r="V27" s="5" t="n">
-        <v>16.81</v>
-      </c>
-      <c r="W27" s="5" t="n">
+      <c r="W27">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="X27">
         <v>18.02</v>
       </c>
-      <c r="X27" s="5" t="n">
+      <c r="Y27">
         <v>16.14</v>
       </c>
-      <c r="Y27" s="5" t="n">
+      <c r="Z27">
         <v>16.22</v>
       </c>
-      <c r="Z27" s="5" t="n">
+      <c r="AA27">
         <v>16.13</v>
       </c>
-      <c r="AA27" s="5" t="n">
+      <c r="AB27">
         <v>16.45</v>
       </c>
-      <c r="AB27" s="5" t="n">
+      <c r="AC27">
         <v>16.05</v>
       </c>
-      <c r="AC27" s="5" t="n">
+      <c r="AD27">
         <v>15.29</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="AE27" s="5" t="n">
+      <c r="AE27">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="AF27">
         <v>14.99</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28">
         <v>90105</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" t="s">
         <v>58</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F28">
         <v>10.11</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="G28">
         <v>8.5</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="H28">
         <v>10.63</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="I28">
         <v>8.73</v>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="J28">
         <v>10.33</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="K28">
         <v>9.48</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="L28">
         <v>9.25</v>
       </c>
-      <c r="L28" s="5" t="n">
-        <v>9.87</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>8.97</v>
-      </c>
-      <c r="N28" s="5" t="n">
+      <c r="M28">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="N28">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="O28">
         <v>8.92</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="P28">
         <v>9.74</v>
       </c>
-      <c r="P28" s="5" t="n">
-        <v>9.04</v>
-      </c>
-      <c r="Q28" s="5" t="n">
+      <c r="Q28">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="R28">
         <v>8.58</v>
       </c>
-      <c r="R28" s="5" t="n">
+      <c r="S28">
         <v>9.51</v>
       </c>
-      <c r="S28" s="5" t="n">
+      <c r="T28">
         <v>8.33</v>
       </c>
-      <c r="T28" s="5" t="n">
+      <c r="U28">
         <v>8.84</v>
       </c>
-      <c r="U28" s="5" t="n">
-        <v>8.88</v>
-      </c>
-      <c r="V28" s="5" t="n">
+      <c r="V28">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="W28">
         <v>10</v>
       </c>
-      <c r="W28" s="5" t="n">
+      <c r="X28">
         <v>10.72</v>
       </c>
-      <c r="X28" s="5" t="n">
+      <c r="Y28">
         <v>9.56</v>
       </c>
-      <c r="Y28" s="5" t="n">
-        <v>9.63</v>
-      </c>
-      <c r="Z28" s="5" t="n">
+      <c r="Z28">
+        <v>9.6300000000000008</v>
+      </c>
+      <c r="AA28">
         <v>9.56</v>
       </c>
-      <c r="AA28" s="5" t="n">
+      <c r="AB28">
         <v>9.76</v>
       </c>
-      <c r="AB28" s="5" t="n">
+      <c r="AC28">
         <v>9.52</v>
       </c>
-      <c r="AC28" s="5" t="n">
+      <c r="AD28">
         <v>9.06</v>
       </c>
-      <c r="AD28" s="5" t="n">
+      <c r="AE28">
         <v>10.75</v>
       </c>
-      <c r="AE28" s="5" t="n">
-        <v>8.88</v>
+      <c r="AF28">
+        <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29">
         <v>101576</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F29">
         <v>41.88</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>35.88</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29">
+        <v>35.880000000000003</v>
+      </c>
+      <c r="H29">
         <v>39.22</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="I29">
         <v>34.68</v>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="J29">
         <v>45.52</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="K29">
         <v>45.13</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="L29">
         <v>45.05</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="M29">
         <v>48.09</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="N29">
         <v>41.04</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="O29">
         <v>42.91</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="P29">
         <v>50.09</v>
       </c>
-      <c r="P29" s="5" t="n">
+      <c r="Q29">
         <v>41.97</v>
       </c>
-      <c r="Q29" s="5" t="n">
+      <c r="R29">
         <v>38.64</v>
       </c>
-      <c r="R29" s="5" t="n">
+      <c r="S29">
         <v>43.92</v>
       </c>
-      <c r="S29" s="5" t="n">
+      <c r="T29">
         <v>36.86</v>
       </c>
-      <c r="T29" s="5" t="n">
+      <c r="U29">
         <v>45.1</v>
       </c>
-      <c r="U29" s="5" t="n">
-        <v>36.63</v>
-      </c>
-      <c r="V29" s="5" t="n">
+      <c r="V29">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="W29">
         <v>54.95</v>
       </c>
-      <c r="W29" s="5" t="n">
+      <c r="X29">
         <v>54.7</v>
       </c>
-      <c r="X29" s="5" t="n">
+      <c r="Y29">
         <v>44.1</v>
       </c>
-      <c r="Y29" s="5" t="n">
+      <c r="Z29">
         <v>45.29</v>
       </c>
-      <c r="Z29" s="5" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="AA29" s="5" t="n">
+      <c r="AA29">
+        <v>37.840000000000003</v>
+      </c>
+      <c r="AB29">
         <v>42.11</v>
       </c>
-      <c r="AB29" s="5" t="n">
+      <c r="AC29">
         <v>71.3</v>
       </c>
-      <c r="AC29" s="5" t="n">
+      <c r="AD29">
         <v>37.33</v>
       </c>
-      <c r="AD29" s="5" t="n">
+      <c r="AE29">
         <v>52.31</v>
       </c>
-      <c r="AE29" s="5" t="n">
+      <c r="AF29">
         <v>41.89</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30">
         <v>101578</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F30">
         <v>34.03</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="G30">
         <v>29.23</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="H30">
         <v>31.51</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="I30">
         <v>28.24</v>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="J30">
         <v>37.18</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="K30">
         <v>37.14</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="L30" s="5" t="n">
+      <c r="L30">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="M30">
         <v>39.14</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="N30">
         <v>33.33</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="O30">
         <v>35.17</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="P30">
         <v>41.63</v>
       </c>
-      <c r="P30" s="5" t="n">
+      <c r="Q30">
         <v>34.72</v>
       </c>
-      <c r="Q30" s="5" t="n">
+      <c r="R30">
         <v>31.77</v>
       </c>
-      <c r="R30" s="5" t="n">
+      <c r="S30">
         <v>35.97</v>
       </c>
-      <c r="S30" s="5" t="n">
+      <c r="T30">
         <v>30.33</v>
       </c>
-      <c r="T30" s="5" t="n">
+      <c r="U30">
         <v>37.17</v>
       </c>
-      <c r="U30" s="5" t="n">
+      <c r="V30">
         <v>29.8</v>
       </c>
-      <c r="V30" s="5" t="n">
+      <c r="W30">
         <v>45</v>
       </c>
-      <c r="W30" s="5" t="n">
+      <c r="X30">
         <v>44.45</v>
       </c>
-      <c r="X30" s="5" t="n">
+      <c r="Y30">
         <v>36.65</v>
       </c>
-      <c r="Y30" s="5" t="n">
+      <c r="Z30">
         <v>37.07</v>
       </c>
-      <c r="Z30" s="5" t="n">
+      <c r="AA30">
         <v>30.34</v>
       </c>
-      <c r="AA30" s="5" t="n">
+      <c r="AB30">
         <v>34.5</v>
       </c>
-      <c r="AB30" s="5" t="n">
+      <c r="AC30">
         <v>60.18</v>
       </c>
-      <c r="AC30" s="5" t="n">
+      <c r="AD30">
         <v>30.41</v>
       </c>
-      <c r="AD30" s="5" t="n">
+      <c r="AE30">
         <v>42.86</v>
       </c>
-      <c r="AE30" s="5" t="n">
+      <c r="AF30">
         <v>34.51</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31">
         <v>101570</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" t="s">
         <v>69</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F31">
         <v>25.03</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="G31">
         <v>21.42</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="H31">
         <v>24.48</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="I31">
         <v>20.77</v>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="J31">
         <v>26.72</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="K31">
         <v>25.66</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="L31">
         <v>26.35</v>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="M31">
         <v>28.5</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="N31">
         <v>24.66</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="O31">
         <v>24.84</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="P31">
         <v>27.24</v>
       </c>
-      <c r="P31" s="5" t="n">
+      <c r="Q31">
         <v>23.72</v>
       </c>
-      <c r="Q31" s="5" t="n">
+      <c r="R31">
         <v>22.27</v>
       </c>
-      <c r="R31" s="5" t="n">
+      <c r="S31">
         <v>25.5</v>
       </c>
-      <c r="S31" s="5" t="n">
+      <c r="T31">
         <v>21.15</v>
       </c>
-      <c r="T31" s="5" t="n">
+      <c r="U31">
         <v>25.62</v>
       </c>
-      <c r="U31" s="5" t="n">
+      <c r="V31">
         <v>21.89</v>
       </c>
-      <c r="V31" s="5" t="n">
+      <c r="W31">
         <v>31.89</v>
       </c>
-      <c r="W31" s="5" t="n">
+      <c r="X31">
         <v>32.61</v>
       </c>
-      <c r="X31" s="5" t="n">
+      <c r="Y31">
         <v>24.15</v>
       </c>
-      <c r="Y31" s="5" t="n">
+      <c r="Z31">
         <v>26.41</v>
       </c>
-      <c r="Z31" s="5" t="n">
+      <c r="AA31">
         <v>23.77</v>
       </c>
-      <c r="AA31" s="5" t="n">
+      <c r="AB31">
         <v>24.66</v>
       </c>
-      <c r="AB31" s="5" t="n">
+      <c r="AC31">
         <v>36.08</v>
       </c>
-      <c r="AC31" s="5" t="n">
+      <c r="AD31">
         <v>22.19</v>
       </c>
-      <c r="AD31" s="5" t="n">
+      <c r="AE31">
         <v>30.12</v>
       </c>
-      <c r="AE31" s="5" t="n">
+      <c r="AF31">
         <v>23.76</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32">
         <v>101622</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" t="s">
         <v>58</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F32">
         <v>276.05</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="G32">
         <v>202.54</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="H32">
         <v>240.09</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="I32">
         <v>259.81</v>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="J32">
         <v>270.92</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="K32">
         <v>244.15</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="L32">
         <v>336.84</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="M32">
         <v>213.38</v>
       </c>
-      <c r="M32" s="5" t="n">
-        <v>266.41</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>276.96</v>
-      </c>
-      <c r="O32" s="5" t="n">
+      <c r="N32">
+        <v>266.41000000000003</v>
+      </c>
+      <c r="O32">
+        <v>276.95999999999998</v>
+      </c>
+      <c r="P32">
         <v>290.86</v>
       </c>
-      <c r="P32" s="5" t="n">
+      <c r="Q32">
         <v>194.05</v>
       </c>
-      <c r="Q32" s="5" t="n">
+      <c r="R32">
         <v>235.31</v>
       </c>
-      <c r="R32" s="5" t="n">
+      <c r="S32">
         <v>238.1</v>
       </c>
-      <c r="S32" s="5" t="n">
+      <c r="T32">
         <v>249.67</v>
       </c>
-      <c r="T32" s="5" t="n">
+      <c r="U32">
         <v>251.33</v>
       </c>
-      <c r="U32" s="5" t="n">
+      <c r="V32">
         <v>196.17</v>
       </c>
-      <c r="V32" s="5" t="n">
+      <c r="W32">
         <v>254.74</v>
       </c>
-      <c r="W32" s="5" t="n">
+      <c r="X32">
         <v>234.89</v>
       </c>
-      <c r="X32" s="5" t="n">
+      <c r="Y32">
         <v>224.6</v>
       </c>
-      <c r="Y32" s="5" t="n">
+      <c r="Z32">
         <v>274.86</v>
       </c>
-      <c r="Z32" s="5" t="n">
+      <c r="AA32">
         <v>181.2</v>
       </c>
-      <c r="AA32" s="5" t="n">
+      <c r="AB32">
         <v>214.1</v>
       </c>
-      <c r="AB32" s="5" t="n">
-        <v>286.66</v>
-      </c>
-      <c r="AC32" s="5" t="n">
+      <c r="AC32">
+        <v>286.66000000000003</v>
+      </c>
+      <c r="AD32">
         <v>209.24</v>
       </c>
-      <c r="AD32" s="5" t="n">
+      <c r="AE32">
         <v>218.72</v>
       </c>
-      <c r="AE32" s="5" t="n">
+      <c r="AF32">
         <v>237.71</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33">
         <v>104031</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F33">
         <v>19.18</v>
       </c>
-      <c r="F33" s="5" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33">
+        <v>16.649999999999999</v>
+      </c>
+      <c r="H33">
         <v>23.1</v>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="I33" s="5" t="n">
+      <c r="I33">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="J33">
         <v>18.61</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="K33">
         <v>21.9</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="L33">
         <v>22.86</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="M33">
         <v>23.73</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="N33">
         <v>20.23</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="O33">
         <v>20.61</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="P33">
         <v>21.6</v>
       </c>
-      <c r="P33" s="5" t="n">
+      <c r="Q33">
         <v>17.37</v>
       </c>
-      <c r="Q33" s="5" t="n">
+      <c r="R33">
         <v>16.7</v>
       </c>
-      <c r="R33" s="5" t="n">
+      <c r="S33">
         <v>20.14</v>
       </c>
-      <c r="S33" s="5" t="n">
+      <c r="T33">
         <v>19.29</v>
       </c>
-      <c r="T33" s="5" t="n">
+      <c r="U33">
         <v>20.41</v>
       </c>
-      <c r="U33" s="5" t="n">
+      <c r="V33">
         <v>22.18</v>
       </c>
-      <c r="V33" s="5" t="n">
+      <c r="W33">
         <v>22.4</v>
       </c>
-      <c r="W33" s="5" t="n">
+      <c r="X33">
         <v>27.3</v>
       </c>
-      <c r="X33" s="5" t="n">
+      <c r="Y33">
         <v>22.08</v>
       </c>
-      <c r="Y33" s="5" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="Z33" s="5" t="n">
+      <c r="Z33">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="AA33">
         <v>20.95</v>
       </c>
-      <c r="AA33" s="5" t="n">
+      <c r="AB33">
         <v>21.67</v>
       </c>
-      <c r="AB33" s="5" t="n">
+      <c r="AC33">
         <v>20.39</v>
       </c>
-      <c r="AC33" s="5" t="n">
+      <c r="AD33">
         <v>20.77</v>
       </c>
-      <c r="AD33" s="5" t="n">
+      <c r="AE33">
         <v>25.05</v>
       </c>
-      <c r="AE33" s="5" t="n">
+      <c r="AF33">
         <v>19.89</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34">
         <v>104046</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F34">
         <v>7.64</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="G34">
         <v>6.71</v>
       </c>
-      <c r="G34" s="5" t="n">
-        <v>8.28</v>
-      </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="I34">
         <v>6.59</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="J34">
         <v>8.43</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="K34">
         <v>7.78</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="L34" s="5" t="n">
+      <c r="L34">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="M34">
         <v>8.61</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="N34">
         <v>7.04</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="O34">
         <v>7.23</v>
       </c>
-      <c r="O34" s="5" t="n">
-        <v>9.97</v>
-      </c>
-      <c r="P34" s="5" t="n">
+      <c r="P34">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="Q34">
         <v>7.02</v>
       </c>
-      <c r="Q34" s="5" t="n">
+      <c r="R34">
         <v>6.54</v>
       </c>
-      <c r="R34" s="5" t="n">
+      <c r="S34">
         <v>7.38</v>
       </c>
-      <c r="S34" s="5" t="n">
+      <c r="T34">
         <v>6.61</v>
       </c>
-      <c r="T34" s="5" t="n">
+      <c r="U34">
         <v>7.12</v>
       </c>
-      <c r="U34" s="5" t="n">
+      <c r="V34">
         <v>7.15</v>
       </c>
-      <c r="V34" s="5" t="n">
+      <c r="W34">
         <v>8.01</v>
       </c>
-      <c r="W34" s="5" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="X34" s="5" t="n">
+      <c r="X34">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="Y34">
         <v>7.84</v>
       </c>
-      <c r="Y34" s="5" t="n">
+      <c r="Z34">
         <v>7.42</v>
       </c>
-      <c r="Z34" s="5" t="n">
+      <c r="AA34">
         <v>7.37</v>
       </c>
-      <c r="AA34" s="5" t="n">
+      <c r="AB34">
         <v>10.56</v>
       </c>
-      <c r="AB34" s="5" t="n">
+      <c r="AC34">
         <v>7.12</v>
       </c>
-      <c r="AC34" s="5" t="n">
+      <c r="AD34">
         <v>7.28</v>
       </c>
-      <c r="AD34" s="5" t="n">
+      <c r="AE34">
         <v>9.14</v>
       </c>
-      <c r="AE34" s="5" t="n">
+      <c r="AF34">
         <v>6.91</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35">
         <v>104062</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F35">
         <v>79.31</v>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>68.96</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35">
+        <v>68.959999999999994</v>
+      </c>
+      <c r="H35">
         <v>66.48</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="I35">
         <v>53.96</v>
       </c>
-      <c r="I35" s="5" t="n">
-        <v>66.54</v>
-      </c>
-      <c r="J35" s="5" t="n">
+      <c r="J35">
+        <v>66.540000000000006</v>
+      </c>
+      <c r="K35">
         <v>72.91</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L35">
         <v>72.53</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="M35">
         <v>91.3</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="N35">
         <v>75.77</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="O35">
         <v>65.34</v>
       </c>
-      <c r="O35" s="5" t="n">
-        <v>74.57</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>75.82</v>
-      </c>
-      <c r="Q35" s="5" t="n">
+      <c r="P35">
+        <v>74.569999999999993</v>
+      </c>
+      <c r="Q35">
+        <v>75.819999999999993</v>
+      </c>
+      <c r="R35">
         <v>72</v>
       </c>
-      <c r="R35" s="5" t="n">
+      <c r="S35">
         <v>74.08</v>
       </c>
-      <c r="S35" s="5" t="n">
+      <c r="T35">
         <v>63.22</v>
       </c>
-      <c r="T35" s="5" t="n">
+      <c r="U35">
         <v>59.85</v>
       </c>
-      <c r="U35" s="5" t="n">
+      <c r="V35">
         <v>67.23</v>
       </c>
-      <c r="V35" s="5" t="n">
+      <c r="W35">
         <v>69.86</v>
       </c>
-      <c r="W35" s="5" t="n">
-        <v>81.04</v>
-      </c>
-      <c r="X35" s="5" t="n">
-        <v>71.96</v>
-      </c>
-      <c r="Y35" s="5" t="n">
+      <c r="X35">
+        <v>81.040000000000006</v>
+      </c>
+      <c r="Y35">
+        <v>71.959999999999994</v>
+      </c>
+      <c r="Z35">
         <v>82.61</v>
       </c>
-      <c r="Z35" s="5" t="n">
+      <c r="AA35">
         <v>63.06</v>
       </c>
-      <c r="AA35" s="5" t="n">
+      <c r="AB35">
         <v>78.25</v>
       </c>
-      <c r="AB35" s="5" t="n">
+      <c r="AC35">
         <v>70.14</v>
       </c>
-      <c r="AC35" s="5" t="n">
+      <c r="AD35">
         <v>67.69</v>
       </c>
-      <c r="AD35" s="5" t="n">
-        <v>78.76</v>
-      </c>
-      <c r="AE35" s="5" t="n">
-        <v>70.01</v>
+      <c r="AE35">
+        <v>78.760000000000005</v>
+      </c>
+      <c r="AF35">
+        <v>70.010000000000005</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36">
         <v>104058</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" t="s">
         <v>63</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F36">
         <v>7.36</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="G36">
         <v>7.05</v>
       </c>
-      <c r="G36" s="5" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I36">
         <v>5.92</v>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="J36">
         <v>7.22</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="K36">
         <v>6.95</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="L36">
         <v>7.37</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="M36">
         <v>9.08</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="N36">
         <v>7.23</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="O36">
         <v>6.79</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="P36">
         <v>6.97</v>
       </c>
-      <c r="P36" s="5" t="n">
+      <c r="Q36">
         <v>6.77</v>
       </c>
-      <c r="Q36" s="5" t="n">
+      <c r="R36">
         <v>6.29</v>
       </c>
-      <c r="R36" s="5" t="n">
+      <c r="S36">
         <v>7.22</v>
       </c>
-      <c r="S36" s="5" t="n">
+      <c r="T36">
         <v>5.98</v>
       </c>
-      <c r="T36" s="5" t="n">
+      <c r="U36">
         <v>6.81</v>
       </c>
-      <c r="U36" s="5" t="n">
+      <c r="V36">
         <v>6.38</v>
       </c>
-      <c r="V36" s="5" t="n">
-        <v>8.29</v>
-      </c>
-      <c r="W36" s="5" t="n">
+      <c r="W36">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="X36">
         <v>8.69</v>
       </c>
-      <c r="X36" s="5" t="n">
+      <c r="Y36">
         <v>6.69</v>
       </c>
-      <c r="Y36" s="5" t="n">
+      <c r="Z36">
         <v>7.4</v>
       </c>
-      <c r="Z36" s="5" t="n">
+      <c r="AA36">
         <v>7.34</v>
       </c>
-      <c r="AA36" s="5" t="n">
+      <c r="AB36">
         <v>7.29</v>
       </c>
-      <c r="AB36" s="5" t="n">
+      <c r="AC36">
         <v>9.01</v>
       </c>
-      <c r="AC36" s="5" t="n">
+      <c r="AD36">
         <v>6.41</v>
       </c>
-      <c r="AD36" s="5" t="n">
-        <v>9.13</v>
-      </c>
-      <c r="AE36" s="5" t="n">
+      <c r="AE36">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="AF36">
         <v>6.87</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37">
         <v>104056</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" t="s">
         <v>78</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F37">
         <v>23.44</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="G37">
         <v>16.98</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="H37">
         <v>37.35</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="I37">
         <v>23.44</v>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="J37">
         <v>23.74</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="K37">
         <v>16.5</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="L37">
         <v>25.05</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="M37">
         <v>30.49</v>
       </c>
-      <c r="M37" s="5" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="N37" s="5" t="n">
+      <c r="N37">
+        <v>17.829999999999998</v>
+      </c>
+      <c r="O37">
         <v>24.02</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="P37">
         <v>17.13</v>
       </c>
-      <c r="P37" s="5" t="n">
+      <c r="Q37">
         <v>20.77</v>
       </c>
-      <c r="Q37" s="5" t="n">
+      <c r="R37">
         <v>18.47</v>
       </c>
-      <c r="R37" s="5" t="n">
+      <c r="S37">
         <v>20.51</v>
       </c>
-      <c r="S37" s="5" t="n">
+      <c r="T37">
         <v>17.57</v>
       </c>
-      <c r="T37" s="5" t="n">
+      <c r="U37">
         <v>26.52</v>
       </c>
-      <c r="U37" s="5" t="n">
+      <c r="V37">
         <v>27.5</v>
       </c>
-      <c r="V37" s="5" t="n">
+      <c r="W37">
         <v>23.89</v>
       </c>
-      <c r="W37" s="5" t="n">
+      <c r="X37">
         <v>33.17</v>
       </c>
-      <c r="X37" s="5" t="n">
+      <c r="Y37">
         <v>15.59</v>
       </c>
-      <c r="Y37" s="5" t="n">
+      <c r="Z37">
         <v>24.3</v>
       </c>
-      <c r="Z37" s="5" t="n">
-        <v>16.06</v>
-      </c>
-      <c r="AA37" s="5" t="n">
+      <c r="AA37">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="AB37">
         <v>34.46</v>
       </c>
-      <c r="AB37" s="5" t="n">
+      <c r="AC37">
         <v>22.26</v>
       </c>
-      <c r="AC37" s="5" t="n">
+      <c r="AD37">
         <v>20.12</v>
       </c>
-      <c r="AD37" s="5" t="n">
+      <c r="AE37">
         <v>28.23</v>
       </c>
-      <c r="AE37" s="5" t="n">
-        <v>16.19</v>
+      <c r="AF37">
+        <v>16.190000000000001</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38">
         <v>104076</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F38">
         <v>48.64</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="G38">
         <v>41.67</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="H38">
         <v>43.2</v>
       </c>
-      <c r="H38" s="5" t="n">
-        <v>33.16</v>
-      </c>
-      <c r="I38" s="5" t="n">
+      <c r="I38">
+        <v>33.159999999999997</v>
+      </c>
+      <c r="J38">
         <v>43.97</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="K38">
         <v>45.65</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="L38">
         <v>47.04</v>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="M38">
         <v>57.94</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="N38">
         <v>46.11</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="O38">
         <v>40.53</v>
       </c>
-      <c r="O38" s="5" t="n">
+      <c r="P38">
         <v>47.29</v>
       </c>
-      <c r="P38" s="5" t="n">
+      <c r="Q38">
         <v>46.43</v>
       </c>
-      <c r="Q38" s="5" t="n">
+      <c r="R38">
         <v>43.4</v>
       </c>
-      <c r="R38" s="5" t="n">
+      <c r="S38">
         <v>45.28</v>
       </c>
-      <c r="S38" s="5" t="n">
+      <c r="T38">
         <v>38.5</v>
       </c>
-      <c r="T38" s="5" t="n">
+      <c r="U38">
         <v>37.25</v>
       </c>
-      <c r="U38" s="5" t="n">
+      <c r="V38">
         <v>41.48</v>
       </c>
-      <c r="V38" s="5" t="n">
+      <c r="W38">
         <v>45.11</v>
       </c>
-      <c r="W38" s="5" t="n">
+      <c r="X38">
         <v>55.34</v>
       </c>
-      <c r="X38" s="5" t="n">
+      <c r="Y38">
         <v>45.71</v>
       </c>
-      <c r="Y38" s="5" t="n">
+      <c r="Z38">
         <v>50.69</v>
       </c>
-      <c r="Z38" s="5" t="n">
+      <c r="AA38">
         <v>40.1</v>
       </c>
-      <c r="AA38" s="5" t="n">
+      <c r="AB38">
         <v>48.94</v>
       </c>
-      <c r="AB38" s="5" t="n">
+      <c r="AC38">
         <v>43.57</v>
       </c>
-      <c r="AC38" s="5" t="n">
+      <c r="AD38">
         <v>42.39</v>
       </c>
-      <c r="AD38" s="5" t="n">
+      <c r="AE38">
         <v>52.29</v>
       </c>
-      <c r="AE38" s="5" t="n">
+      <c r="AF38">
         <v>42.73</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39">
         <v>104060</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" t="s">
         <v>33</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>9.04</v>
-      </c>
-      <c r="F39" s="5" t="n">
+      <c r="E39" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F39">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="G39">
         <v>8.26</v>
       </c>
-      <c r="G39" s="5" t="n">
-        <v>9.62</v>
-      </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="I39">
         <v>8.15</v>
       </c>
-      <c r="I39" s="5" t="n">
+      <c r="J39">
         <v>9.73</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="K39">
         <v>9.17</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v>9.53</v>
-      </c>
-      <c r="L39" s="5" t="n">
+      <c r="L39">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="M39">
         <v>9.85</v>
       </c>
-      <c r="M39" s="5" t="n">
-        <v>8.55</v>
-      </c>
-      <c r="N39" s="5" t="n">
+      <c r="N39">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="O39">
         <v>8.68</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="P39">
         <v>9.19</v>
       </c>
-      <c r="P39" s="5" t="n">
+      <c r="Q39">
         <v>8.5</v>
       </c>
-      <c r="Q39" s="5" t="n">
+      <c r="R39">
         <v>8.09</v>
       </c>
-      <c r="R39" s="5" t="n">
+      <c r="S39">
         <v>8.82</v>
       </c>
-      <c r="S39" s="5" t="n">
+      <c r="T39">
         <v>8.19</v>
       </c>
-      <c r="T39" s="5" t="n">
+      <c r="U39">
         <v>8.61</v>
       </c>
-      <c r="U39" s="5" t="n">
-        <v>8.62</v>
-      </c>
-      <c r="V39" s="5" t="n">
+      <c r="V39">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="W39">
         <v>9.35</v>
       </c>
-      <c r="W39" s="5" t="n">
+      <c r="X39">
         <v>11.18</v>
       </c>
-      <c r="X39" s="5" t="n">
+      <c r="Y39">
         <v>9.24</v>
       </c>
-      <c r="Y39" s="5" t="n">
+      <c r="Z39">
         <v>8.86</v>
       </c>
-      <c r="Z39" s="5" t="n">
+      <c r="AA39">
         <v>8.81</v>
       </c>
-      <c r="AA39" s="5" t="n">
+      <c r="AB39">
         <v>10.01</v>
       </c>
-      <c r="AB39" s="5" t="n">
+      <c r="AC39">
         <v>8.6</v>
       </c>
-      <c r="AC39" s="5" t="n">
+      <c r="AD39">
         <v>8.74</v>
       </c>
-      <c r="AD39" s="5" t="n">
+      <c r="AE39">
         <v>10.34</v>
       </c>
-      <c r="AE39" s="5" t="n">
+      <c r="AF39">
         <v>8.41</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40">
         <v>104085</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" t="s">
         <v>81</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F40">
         <v>57.91</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="G40">
         <v>50.09</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="H40">
         <v>49.98</v>
       </c>
-      <c r="H40" s="5" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="I40" s="5" t="n">
+      <c r="I40">
+        <v>39.090000000000003</v>
+      </c>
+      <c r="J40">
         <v>50.81</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="K40">
         <v>53.85</v>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="L40">
         <v>55.09</v>
       </c>
-      <c r="L40" s="5" t="n">
+      <c r="M40">
         <v>68.8</v>
       </c>
-      <c r="M40" s="5" t="n">
+      <c r="N40">
         <v>55.37</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="O40">
         <v>47.9</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="P40">
         <v>55.91</v>
       </c>
-      <c r="P40" s="5" t="n">
+      <c r="Q40">
         <v>55.83</v>
       </c>
-      <c r="Q40" s="5" t="n">
+      <c r="R40">
         <v>52.49</v>
       </c>
-      <c r="R40" s="5" t="n">
+      <c r="S40">
         <v>53.87</v>
       </c>
-      <c r="S40" s="5" t="n">
+      <c r="T40">
         <v>46.07</v>
       </c>
-      <c r="T40" s="5" t="n">
+      <c r="U40">
         <v>43.73</v>
       </c>
-      <c r="U40" s="5" t="n">
+      <c r="V40">
         <v>49.22</v>
       </c>
-      <c r="V40" s="5" t="n">
+      <c r="W40">
         <v>52.8</v>
       </c>
-      <c r="W40" s="5" t="n">
+      <c r="X40">
         <v>63.35</v>
       </c>
-      <c r="X40" s="5" t="n">
+      <c r="Y40">
         <v>53.84</v>
       </c>
-      <c r="Y40" s="5" t="n">
+      <c r="Z40">
         <v>60.85</v>
       </c>
-      <c r="Z40" s="5" t="n">
+      <c r="AA40">
         <v>47.15</v>
       </c>
-      <c r="AA40" s="5" t="n">
+      <c r="AB40">
         <v>58.17</v>
       </c>
-      <c r="AB40" s="5" t="n">
+      <c r="AC40">
         <v>51.93</v>
       </c>
-      <c r="AC40" s="5" t="n">
+      <c r="AD40">
         <v>50.23</v>
       </c>
-      <c r="AD40" s="5" t="n">
+      <c r="AE40">
         <v>60.71</v>
       </c>
-      <c r="AE40" s="5" t="n">
+      <c r="AF40">
         <v>51.18</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41">
         <v>99063</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F41">
         <v>10.16</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="G41">
         <v>8.49</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="H41">
         <v>10.09</v>
       </c>
-      <c r="H41" s="5" t="n">
-        <v>8.54</v>
-      </c>
-      <c r="I41" s="5" t="n">
+      <c r="I41">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="J41">
         <v>10.23</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="K41">
         <v>9.86</v>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="L41">
         <v>10.17</v>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="M41">
         <v>11.12</v>
       </c>
-      <c r="M41" s="5" t="n">
-        <v>9.45</v>
-      </c>
-      <c r="N41" s="5" t="n">
+      <c r="N41">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="O41">
         <v>9.66</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="P41">
         <v>10.39</v>
       </c>
-      <c r="P41" s="5" t="n">
-        <v>8.95</v>
-      </c>
-      <c r="Q41" s="5" t="n">
-        <v>8.7</v>
-      </c>
-      <c r="R41" s="5" t="n">
+      <c r="Q41">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="R41">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="S41">
         <v>10</v>
       </c>
-      <c r="S41" s="5" t="n">
+      <c r="T41">
         <v>8.18</v>
       </c>
-      <c r="T41" s="5" t="n">
+      <c r="U41">
         <v>9.76</v>
       </c>
-      <c r="U41" s="5" t="n">
+      <c r="V41">
         <v>8.68</v>
       </c>
-      <c r="V41" s="5" t="n">
+      <c r="W41">
         <v>12.18</v>
       </c>
-      <c r="W41" s="5" t="n">
+      <c r="X41">
         <v>12.62</v>
       </c>
-      <c r="X41" s="5" t="n">
-        <v>9.28</v>
-      </c>
-      <c r="Y41" s="5" t="n">
+      <c r="Y41">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="Z41">
         <v>10.63</v>
       </c>
-      <c r="Z41" s="5" t="n">
+      <c r="AA41">
         <v>9.77</v>
       </c>
-      <c r="AA41" s="5" t="n">
+      <c r="AB41">
         <v>9.69</v>
       </c>
-      <c r="AB41" s="5" t="n">
+      <c r="AC41">
         <v>12.72</v>
       </c>
-      <c r="AC41" s="5" t="n">
+      <c r="AD41">
         <v>8.68</v>
       </c>
-      <c r="AD41" s="5" t="n">
+      <c r="AE41">
         <v>11.8</v>
       </c>
-      <c r="AE41" s="5" t="n">
+      <c r="AF41">
         <v>9.43</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42">
         <v>97983</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" t="s">
         <v>85</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F42">
         <v>679.15</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="G42">
         <v>402.39</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="H42">
         <v>679.35</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="I42">
         <v>666.45</v>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="J42">
         <v>547.66</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="K42">
         <v>670.08</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>545.82</v>
-      </c>
-      <c r="L42" s="5" t="n">
+      <c r="L42">
+        <v>545.82000000000005</v>
+      </c>
+      <c r="M42">
         <v>538.91</v>
       </c>
-      <c r="M42" s="5" t="n">
+      <c r="N42">
         <v>667.17</v>
       </c>
-      <c r="N42" s="5" t="n">
-        <v>579.82</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>539.92</v>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v>572.44</v>
-      </c>
-      <c r="Q42" s="5" t="n">
+      <c r="O42">
+        <v>579.82000000000005</v>
+      </c>
+      <c r="P42">
+        <v>539.91999999999996</v>
+      </c>
+      <c r="Q42">
+        <v>572.44000000000005</v>
+      </c>
+      <c r="R42">
         <v>662.46</v>
       </c>
-      <c r="R42" s="5" t="n">
+      <c r="S42">
         <v>530.25</v>
       </c>
-      <c r="S42" s="5" t="n">
+      <c r="T42">
         <v>659.69</v>
       </c>
-      <c r="T42" s="5" t="n">
+      <c r="U42">
         <v>442.14</v>
       </c>
-      <c r="U42" s="5" t="n">
+      <c r="V42">
         <v>505.67</v>
       </c>
-      <c r="V42" s="5" t="n">
+      <c r="W42">
         <v>677.41</v>
       </c>
-      <c r="W42" s="5" t="n">
+      <c r="X42">
         <v>651.89</v>
       </c>
-      <c r="X42" s="5" t="n">
-        <v>527.42</v>
-      </c>
-      <c r="Y42" s="5" t="n">
+      <c r="Y42">
+        <v>527.41999999999996</v>
+      </c>
+      <c r="Z42">
         <v>496.4</v>
       </c>
-      <c r="Z42" s="5" t="n">
+      <c r="AA42">
         <v>678.58</v>
       </c>
-      <c r="AA42" s="5" t="n">
+      <c r="AB42">
         <v>563.48</v>
       </c>
-      <c r="AB42" s="5" t="n">
+      <c r="AC42">
         <v>674</v>
       </c>
-      <c r="AC42" s="5" t="n">
+      <c r="AD42">
         <v>665.7</v>
       </c>
-      <c r="AD42" s="5" t="n">
+      <c r="AE42">
         <v>678.85</v>
       </c>
-      <c r="AE42" s="5" t="n">
+      <c r="AF42">
         <v>505.16</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43">
         <v>98410</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" t="s">
         <v>63</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F43">
         <v>1709.58</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="G43">
         <v>1112.17</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="H43">
         <v>1604.39</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="I43">
         <v>1581.76</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="J43">
         <v>1325.71</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="K43">
         <v>1441.48</v>
       </c>
-      <c r="K43" s="5" t="n">
+      <c r="L43">
         <v>1359.44</v>
       </c>
-      <c r="L43" s="5" t="n">
+      <c r="M43">
         <v>1305.48</v>
       </c>
-      <c r="M43" s="5" t="n">
+      <c r="N43">
         <v>1483.63</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="O43">
         <v>1348.99</v>
       </c>
-      <c r="O43" s="5" t="n">
+      <c r="P43">
         <v>1301.21</v>
       </c>
-      <c r="P43" s="5" t="n">
-        <v>1292.85</v>
-      </c>
-      <c r="Q43" s="5" t="n">
+      <c r="Q43">
+        <v>1292.8499999999999</v>
+      </c>
+      <c r="R43">
         <v>1463.34</v>
       </c>
-      <c r="R43" s="5" t="n">
+      <c r="S43">
         <v>1406.46</v>
       </c>
-      <c r="S43" s="5" t="n">
+      <c r="T43">
         <v>1342.79</v>
       </c>
-      <c r="T43" s="5" t="n">
+      <c r="U43">
         <v>1126.56</v>
       </c>
-      <c r="U43" s="5" t="n">
+      <c r="V43">
         <v>1329.8</v>
       </c>
-      <c r="V43" s="5" t="n">
+      <c r="W43">
         <v>1456.81</v>
       </c>
-      <c r="W43" s="5" t="n">
+      <c r="X43">
         <v>1493.31</v>
       </c>
-      <c r="X43" s="5" t="n">
+      <c r="Y43">
         <v>1268.49</v>
       </c>
-      <c r="Y43" s="5" t="n">
+      <c r="Z43">
         <v>1410.51</v>
       </c>
-      <c r="Z43" s="5" t="n">
+      <c r="AA43">
         <v>1673.25</v>
       </c>
-      <c r="AA43" s="5" t="n">
+      <c r="AB43">
         <v>1337.73</v>
       </c>
-      <c r="AB43" s="5" t="n">
+      <c r="AC43">
         <v>1501.56</v>
       </c>
-      <c r="AC43" s="5" t="n">
+      <c r="AD43">
         <v>1407.41</v>
       </c>
-      <c r="AD43" s="5" t="n">
+      <c r="AE43">
         <v>1441.77</v>
       </c>
-      <c r="AE43" s="5" t="n">
+      <c r="AF43">
         <v>1268.06</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>84</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44">
         <v>98050</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" t="s">
         <v>33</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F44">
         <v>375.96</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="G44">
         <v>221.07</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="H44">
         <v>376.64</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="I44">
         <v>369.74</v>
       </c>
-      <c r="I44" s="5" t="n">
+      <c r="J44">
         <v>302.17</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="K44">
         <v>372.24</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="L44">
         <v>301.73</v>
       </c>
-      <c r="L44" s="5" t="n">
-        <v>298.21</v>
-      </c>
-      <c r="M44" s="5" t="n">
+      <c r="M44">
+        <v>298.20999999999998</v>
+      </c>
+      <c r="N44">
         <v>370.93</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="O44">
         <v>320.94</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="P44">
         <v>298.26</v>
       </c>
-      <c r="P44" s="5" t="n">
+      <c r="Q44">
         <v>317.27</v>
       </c>
-      <c r="Q44" s="5" t="n">
+      <c r="R44">
         <v>368.26</v>
       </c>
-      <c r="R44" s="5" t="n">
+      <c r="S44">
         <v>292.3</v>
       </c>
-      <c r="S44" s="5" t="n">
+      <c r="T44">
         <v>367</v>
       </c>
-      <c r="T44" s="5" t="n">
+      <c r="U44">
         <v>243.59</v>
       </c>
-      <c r="U44" s="5" t="n">
-        <v>278.84</v>
-      </c>
-      <c r="V44" s="5" t="n">
+      <c r="V44">
+        <v>278.83999999999997</v>
+      </c>
+      <c r="W44">
         <v>376.25</v>
       </c>
-      <c r="W44" s="5" t="n">
+      <c r="X44">
         <v>361.55</v>
       </c>
-      <c r="X44" s="5" t="n">
+      <c r="Y44">
         <v>291.56</v>
       </c>
-      <c r="Y44" s="5" t="n">
-        <v>272.96</v>
-      </c>
-      <c r="Z44" s="5" t="n">
+      <c r="Z44">
+        <v>272.95999999999998</v>
+      </c>
+      <c r="AA44">
         <v>375.35</v>
       </c>
-      <c r="AA44" s="5" t="n">
+      <c r="AB44">
         <v>311.43</v>
       </c>
-      <c r="AB44" s="5" t="n">
+      <c r="AC44">
         <v>374.16</v>
       </c>
-      <c r="AC44" s="5" t="n">
+      <c r="AD44">
         <v>369.99</v>
       </c>
-      <c r="AD44" s="5" t="n">
+      <c r="AE44">
         <v>377.1</v>
       </c>
-      <c r="AE44" s="5" t="n">
+      <c r="AF44">
         <v>278.74</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45">
         <v>95676</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" t="s">
         <v>89</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F45">
         <v>170.65</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="G45">
         <v>100.59</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="H45">
         <v>171.21</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="I45">
         <v>168.15</v>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="J45">
         <v>136.06</v>
       </c>
-      <c r="J45" s="5" t="n">
+      <c r="K45">
         <v>170.05</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="L45">
         <v>137.56</v>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="M45">
         <v>136.12</v>
       </c>
-      <c r="M45" s="5" t="n">
+      <c r="N45">
         <v>169.92</v>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="O45">
         <v>146.29</v>
       </c>
-      <c r="O45" s="5" t="n">
-        <v>134.92</v>
-      </c>
-      <c r="P45" s="5" t="n">
+      <c r="P45">
+        <v>134.91999999999999</v>
+      </c>
+      <c r="Q45">
         <v>143.82</v>
       </c>
-      <c r="Q45" s="5" t="n">
+      <c r="R45">
         <v>168.5</v>
       </c>
-      <c r="R45" s="5" t="n">
+      <c r="S45">
         <v>132.13</v>
       </c>
-      <c r="S45" s="5" t="n">
+      <c r="T45">
         <v>167.58</v>
       </c>
-      <c r="T45" s="5" t="n">
+      <c r="U45">
         <v>110.47</v>
       </c>
-      <c r="U45" s="5" t="n">
+      <c r="V45">
         <v>125.52</v>
       </c>
-      <c r="V45" s="5" t="n">
+      <c r="W45">
         <v>174.06</v>
       </c>
-      <c r="W45" s="5" t="n">
+      <c r="X45">
         <v>166.41</v>
       </c>
-      <c r="X45" s="5" t="n">
+      <c r="Y45">
         <v>131.26</v>
       </c>
-      <c r="Y45" s="5" t="n">
+      <c r="Z45">
         <v>123.64</v>
       </c>
-      <c r="Z45" s="5" t="n">
+      <c r="AA45">
         <v>170.51</v>
       </c>
-      <c r="AA45" s="5" t="n">
-        <v>140.92</v>
-      </c>
-      <c r="AB45" s="5" t="n">
+      <c r="AB45">
+        <v>140.91999999999999</v>
+      </c>
+      <c r="AC45">
         <v>171.98</v>
       </c>
-      <c r="AC45" s="5" t="n">
+      <c r="AD45">
         <v>168.57</v>
       </c>
-      <c r="AD45" s="5" t="n">
+      <c r="AE45">
         <v>174.95</v>
       </c>
-      <c r="AE45" s="5" t="n">
+      <c r="AF45">
         <v>127.18</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46">
         <v>95673</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" t="s">
         <v>63</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F46">
         <v>128.96</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="G46">
         <v>127.51</v>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="H46" s="5" t="n">
+      <c r="H46">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="I46">
         <v>124.88</v>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="J46">
         <v>182.38</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="K46">
         <v>127.98</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="L46">
         <v>129.35</v>
       </c>
-      <c r="L46" s="5" t="n">
-        <v>130.67</v>
-      </c>
-      <c r="M46" s="5" t="n">
+      <c r="M46">
+        <v>130.66999999999999</v>
+      </c>
+      <c r="N46">
         <v>127.72</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="O46">
         <v>127.7</v>
       </c>
-      <c r="O46" s="5" t="n">
+      <c r="P46">
         <v>161.06</v>
       </c>
-      <c r="P46" s="5" t="n">
+      <c r="Q46">
         <v>125.43</v>
       </c>
-      <c r="Q46" s="5" t="n">
+      <c r="R46">
         <v>125.42</v>
       </c>
-      <c r="R46" s="5" t="n">
-        <v>128.39</v>
-      </c>
-      <c r="S46" s="5" t="n">
+      <c r="S46">
+        <v>128.38999999999999</v>
+      </c>
+      <c r="T46">
         <v>123.85</v>
       </c>
-      <c r="T46" s="5" t="n">
+      <c r="U46">
         <v>127.76</v>
       </c>
-      <c r="U46" s="5" t="n">
+      <c r="V46">
         <v>125.57</v>
       </c>
-      <c r="V46" s="5" t="n">
-        <v>134.58</v>
-      </c>
-      <c r="W46" s="5" t="n">
+      <c r="W46">
+        <v>134.58000000000001</v>
+      </c>
+      <c r="X46">
         <v>285.83</v>
       </c>
-      <c r="X46" s="5" t="n">
+      <c r="Y46">
         <v>125.84</v>
       </c>
-      <c r="Y46" s="5" t="n">
+      <c r="Z46">
         <v>130.03</v>
       </c>
-      <c r="Z46" s="5" t="n">
+      <c r="AA46">
         <v>128.72</v>
       </c>
-      <c r="AA46" s="5" t="n">
+      <c r="AB46">
         <v>181.28</v>
       </c>
-      <c r="AB46" s="5" t="n">
+      <c r="AC46">
         <v>176.56</v>
       </c>
-      <c r="AC46" s="5" t="n">
+      <c r="AD46">
         <v>125.55</v>
       </c>
-      <c r="AD46" s="5" t="n">
-        <v>135.95</v>
-      </c>
-      <c r="AE46" s="5" t="n">
+      <c r="AE46">
+        <v>135.94999999999999</v>
+      </c>
+      <c r="AF46">
         <v>128.28</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47">
         <v>95634</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F47">
         <v>236.83</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="G47">
         <v>212.91</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="H47">
         <v>212.22</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="I47">
         <v>183.69</v>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="J47">
         <v>202.89</v>
       </c>
-      <c r="J47" s="5" t="n">
+      <c r="K47">
         <v>215.21</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="L47">
         <v>224.75</v>
       </c>
-      <c r="L47" s="5" t="n">
+      <c r="M47">
         <v>265.24</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="N47">
         <v>224.56</v>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="O47">
         <v>206.55</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="P47">
         <v>213.99</v>
       </c>
-      <c r="P47" s="5" t="n">
+      <c r="Q47">
         <v>213.85</v>
       </c>
-      <c r="Q47" s="5" t="n">
+      <c r="R47">
         <v>200.9</v>
       </c>
-      <c r="R47" s="5" t="n">
+      <c r="S47">
         <v>233.42</v>
       </c>
-      <c r="S47" s="5" t="n">
+      <c r="T47">
         <v>195.75</v>
       </c>
-      <c r="T47" s="5" t="n">
+      <c r="U47">
         <v>209.1</v>
       </c>
-      <c r="U47" s="5" t="n">
+      <c r="V47">
         <v>205.72</v>
       </c>
-      <c r="V47" s="5" t="n">
+      <c r="W47">
         <v>223.78</v>
       </c>
-      <c r="W47" s="5" t="n">
+      <c r="X47">
         <v>237.65</v>
       </c>
-      <c r="X47" s="5" t="n">
+      <c r="Y47">
         <v>190.56</v>
       </c>
-      <c r="Y47" s="5" t="n">
+      <c r="Z47">
         <v>221.52</v>
       </c>
-      <c r="Z47" s="5" t="n">
+      <c r="AA47">
         <v>201.04</v>
       </c>
-      <c r="AA47" s="5" t="n">
+      <c r="AB47">
         <v>237.45</v>
       </c>
-      <c r="AB47" s="5" t="n">
+      <c r="AC47">
         <v>216.4</v>
       </c>
-      <c r="AC47" s="5" t="n">
+      <c r="AD47">
         <v>202.82</v>
       </c>
-      <c r="AD47" s="5" t="n">
+      <c r="AE47">
         <v>239.64</v>
       </c>
-      <c r="AE47" s="5" t="n">
+      <c r="AF47">
         <v>210.77</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48">
         <v>100977</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" t="s">
         <v>93</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" t="s">
         <v>58</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F48">
         <v>8.56</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="G48">
         <v>7.66</v>
       </c>
-      <c r="G48" s="5" t="n">
-        <v>8.78</v>
-      </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="I48">
         <v>7.84</v>
       </c>
-      <c r="I48" s="5" t="n">
+      <c r="J48">
         <v>8.16</v>
       </c>
-      <c r="J48" s="5" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="K48" s="5" t="n">
+      <c r="K48">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="L48">
         <v>7.98</v>
       </c>
-      <c r="L48" s="5" t="n">
+      <c r="M48">
         <v>8.07</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="N48">
         <v>7.96</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="O48">
         <v>7.87</v>
       </c>
-      <c r="O48" s="5" t="n">
+      <c r="P48">
         <v>8.09</v>
       </c>
-      <c r="P48" s="5" t="n">
+      <c r="Q48">
         <v>7.7</v>
       </c>
-      <c r="Q48" s="5" t="n">
-        <v>8.05</v>
-      </c>
-      <c r="R48" s="5" t="n">
-        <v>8.12</v>
-      </c>
-      <c r="S48" s="5" t="n">
+      <c r="R48">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="S48">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="T48">
         <v>7.48</v>
       </c>
-      <c r="T48" s="5" t="n">
+      <c r="U48">
         <v>7.76</v>
       </c>
-      <c r="U48" s="5" t="n">
+      <c r="V48">
         <v>7.61</v>
       </c>
-      <c r="V48" s="5" t="n">
+      <c r="W48">
         <v>8.27</v>
       </c>
-      <c r="W48" s="5" t="n">
-        <v>9.3</v>
-      </c>
-      <c r="X48" s="5" t="n">
+      <c r="X48">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Y48">
         <v>8.06</v>
       </c>
-      <c r="Y48" s="5" t="n">
+      <c r="Z48">
         <v>8.34</v>
       </c>
-      <c r="Z48" s="5" t="n">
-        <v>8.37</v>
-      </c>
-      <c r="AA48" s="5" t="n">
-        <v>8.45</v>
-      </c>
-      <c r="AB48" s="5" t="n">
+      <c r="AA48">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="AB48">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="AC48">
         <v>8.49</v>
       </c>
-      <c r="AC48" s="5" t="n">
+      <c r="AD48">
         <v>7.89</v>
       </c>
-      <c r="AD48" s="5" t="n">
-        <v>8.46</v>
-      </c>
-      <c r="AE48" s="5" t="n">
+      <c r="AE48">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="AF48">
         <v>8.43</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49">
         <v>97914</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" t="s">
         <v>95</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="3">
+        <v>45901</v>
+      </c>
+      <c r="F49">
         <v>3.32</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="G49">
         <v>2.97</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="H49">
         <v>3.35</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="I49">
         <v>3.03</v>
       </c>
-      <c r="I49" s="5" t="n">
+      <c r="J49">
         <v>3.06</v>
       </c>
-      <c r="J49" s="5" t="n">
+      <c r="K49">
         <v>3.14</v>
       </c>
-      <c r="K49" s="5" t="n">
+      <c r="L49">
         <v>3.07</v>
       </c>
-      <c r="L49" s="5" t="n">
+      <c r="M49">
         <v>3.07</v>
       </c>
-      <c r="M49" s="5" t="n">
+      <c r="N49">
         <v>3.07</v>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="O49">
         <v>3.03</v>
       </c>
-      <c r="O49" s="5" t="n">
+      <c r="P49">
         <v>3.05</v>
       </c>
-      <c r="P49" s="5" t="n">
+      <c r="Q49">
         <v>2.96</v>
       </c>
-      <c r="Q49" s="5" t="n">
+      <c r="R49">
         <v>3.16</v>
       </c>
-      <c r="R49" s="5" t="n">
+      <c r="S49">
         <v>3.17</v>
       </c>
-      <c r="S49" s="5" t="n">
+      <c r="T49">
         <v>2.88</v>
       </c>
-      <c r="T49" s="5" t="n">
+      <c r="U49">
         <v>3</v>
       </c>
-      <c r="U49" s="5" t="n">
+      <c r="V49">
         <v>2.89</v>
       </c>
-      <c r="V49" s="5" t="n">
+      <c r="W49">
         <v>3.16</v>
       </c>
-      <c r="W49" s="5" t="n">
+      <c r="X49">
         <v>3.55</v>
       </c>
-      <c r="X49" s="5" t="n">
+      <c r="Y49">
         <v>3.05</v>
       </c>
-      <c r="Y49" s="5" t="n">
+      <c r="Z49">
         <v>3.19</v>
       </c>
-      <c r="Z49" s="5" t="n">
+      <c r="AA49">
         <v>3.24</v>
       </c>
-      <c r="AA49" s="5" t="n">
+      <c r="AB49">
         <v>3.15</v>
       </c>
-      <c r="AB49" s="5" t="n">
+      <c r="AC49">
         <v>3.22</v>
       </c>
-      <c r="AC49" s="5" t="n">
+      <c r="AD49">
         <v>3.01</v>
       </c>
-      <c r="AD49" s="5" t="n">
+      <c r="AE49">
         <v>3.18</v>
       </c>
-      <c r="AE49" s="5" t="n">
+      <c r="AF49">
         <v>3.34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE1842"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555556" right="0.511805555555556" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <autoFilter ref="A1:AF1842" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -5324,387 +5401,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="78130ffc-16ea-4ebe-b633-218d21785438">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Moeda xmlns="78130ffc-16ea-4ebe-b633-218d21785438" xsi:nil="true"/>
-    <TaxCatchAll xmlns="f67ef1d0-fd11-4513-a7cd-19c7c2a973db" xsi:nil="true"/>
-    <TESTE xmlns="78130ffc-16ea-4ebe-b633-218d21785438" xsi:nil="true"/>
-    <A xmlns="78130ffc-16ea-4ebe-b633-218d21785438">B</A>
-    <AA xmlns="78130ffc-16ea-4ebe-b633-218d21785438" xsi:nil="true"/>
-    <AAA xmlns="78130ffc-16ea-4ebe-b633-218d21785438" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E81875FA0D4ED14BBFCFE1D80B0EA062" ma:contentTypeVersion="28" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="19b1aab68b63e8dd18c139a986112f54">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="78130ffc-16ea-4ebe-b633-218d21785438" xmlns:ns3="f67ef1d0-fd11-4513-a7cd-19c7c2a973db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="82423c123054fb9ba27fd104c716423b" ns2:_="" ns3:_="">
-    <xsd:import namespace="78130ffc-16ea-4ebe-b633-218d21785438"/>
-    <xsd:import namespace="f67ef1d0-fd11-4513-a7cd-19c7c2a973db"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:Moeda" minOccurs="0"/>
-                <xsd:element ref="ns2:A" minOccurs="0"/>
-                <xsd:element ref="ns2:AA" minOccurs="0"/>
-                <xsd:element ref="ns2:AAA" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74CountryOrRegion" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74State" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74City" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74PostalCode" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74Street" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74GeoLoc" minOccurs="0"/>
-                <xsd:element ref="ns2:d0449b80-e6da-493c-9508-34c90d9f5a74DispName" minOccurs="0"/>
-                <xsd:element ref="ns2:TESTE" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="78130ffc-16ea-4ebe-b633-218d21785438" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="36c7280b-aa8e-499f-8fdb-b794955743f3" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Moeda" ma:index="23" nillable="true" ma:displayName="Moeda" ma:format="R$ 123.456,00 (Brasil)" ma:LCID="1046" ma:internalName="Moeda">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Currency"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="A" ma:index="24" nillable="true" ma:displayName="A" ma:default="B" ma:format="Dropdown" ma:internalName="A">
-      <xsd:simpleType>
-        <xsd:union memberTypes="dms:Text">
-          <xsd:simpleType>
-            <xsd:restriction base="dms:Choice">
-              <xsd:enumeration value="A"/>
-              <xsd:enumeration value="B"/>
-              <xsd:enumeration value="Escolha 3 "/>
-            </xsd:restriction>
-          </xsd:simpleType>
-        </xsd:union>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AA" ma:index="25" nillable="true" ma:displayName="AA" ma:format="Dropdown" ma:list="78130ffc-16ea-4ebe-b633-218d21785438" ma:internalName="AA" ma:showField="Title">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Lookup"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="AAA" ma:index="26" nillable="true" ma:displayName="AAA" ma:format="Dropdown" ma:internalName="AAA">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74CountryOrRegion" ma:index="27" nillable="true" ma:displayName="AAA: País/Região" ma:internalName="CountryOrRegion" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74State" ma:index="28" nillable="true" ma:displayName="AAA: Estado" ma:internalName="State" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74City" ma:index="29" nillable="true" ma:displayName="AAA: Cidade" ma:internalName="City" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74PostalCode" ma:index="30" nillable="true" ma:displayName="AAA: CEP" ma:internalName="PostalCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74Street" ma:index="31" nillable="true" ma:displayName="AAA: Rua" ma:internalName="Street" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74GeoLoc" ma:index="32" nillable="true" ma:displayName="AAA: Coordenadas" ma:internalName="GeoLoc" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="d0449b80-e6da-493c-9508-34c90d9f5a74DispName" ma:index="33" nillable="true" ma:displayName="AAA: Nome" ma:internalName="DispName" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TESTE" ma:index="34" nillable="true" ma:displayName="TESTE" ma:format="Dropdown" ma:internalName="TESTE">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Escolha 1"/>
-          <xsd:enumeration value="Escolha 2"/>
-          <xsd:enumeration value="Escolha 3 "/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="35" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f67ef1d0-fd11-4513-a7cd-19c7c2a973db" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b4ae82a1-6ce2-4f96-884f-dd42ffed8191}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f67ef1d0-fd11-4513-a7cd-19c7c2a973db">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5612BE4F-A317-4D81-B292-EEF6D316DE13}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE04C5A-B143-498B-8428-07F644BDF37D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="78130ffc-16ea-4ebe-b633-218d21785438"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f67ef1d0-fd11-4513-a7cd-19c7c2a973db"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{901AE5F0-C241-49DB-AF74-F9B574C903DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="78130ffc-16ea-4ebe-b633-218d21785438"/>
-    <ds:schemaRef ds:uri="f67ef1d0-fd11-4513-a7cd-19c7c2a973db"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>